--- a/Data/IPPrimeminister.xlsx
+++ b/Data/IPPrimeminister.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,161 +472,161 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Who appoints the Prime Minister of India?</t>
+          <t>Which Prime Minister introduced the slogan 'Minimum Government, Maximum Governance'?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The President formally appoints the PM, usually the leader of the majority in Lok Sabha.</t>
+          <t>It was part of his 2014 election campaign vision.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution deals with the Prime Minister?</t>
+          <t>Which Prime Minister faced the most number of no-confidence motions?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Article 78</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Article 75 provides for the appointment of the Prime Minister and other ministers.</t>
+          <t>She faced the most no-confidence motions during her tenure.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Prime Minister is the head of which body?</t>
+          <t>In the case of death or resignation of Prime Minister, who appoints the new PM?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>The PM is the head of the Council of Ministers and leads the executive branch.</t>
+          <t>The President appoints the new Prime Minister based on majority support.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Prime Minister communicates to the President all decisions of the Council of Ministers under which Article?</t>
+          <t>Which Prime Minister launched the 20-Point Programme in 1975?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Article 78</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Article 78</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>It is the duty of the PM to inform the President of all cabinet decisions.</t>
+          <t>It was a socio-economic initiative launched during the Emergency.</t>
         </is>
       </c>
     </row>
@@ -672,851 +672,835 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Prime Minister must be a member of which House?</t>
+          <t>Which PM passed away while in office outside India?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Only Lok Sabha</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>The PM can be a member of either Lok Sabha or Rajya Sabha.</t>
+          <t>He died in Tashkent (USSR) after signing the Tashkent Agreement in 1966.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What happens if the Prime Minister loses majority support in Lok Sabha?</t>
+          <t>Who appoints the Prime Minister of India?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dismissed by President</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Resigns</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Continues till term ends</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Impeached</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Resigns</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Losing majority means the PM must resign.</t>
+          <t>The President formally appoints the PM, usually the leader of the majority in Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which of the following is a discretionary power of the President regarding the Prime Minister?</t>
+          <t>Which Prime Minister gave the slogan 'Garibi Hatao'?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dismissal</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Appointment when no party has majority</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Salary fixation</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Policy review</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Appointment when no party has majority</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>In case of no clear majority, President has discretion in appointing the PM.</t>
+          <t>She gave this slogan during the 1971 election campaign.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Prime Minister is described as which of the following?</t>
+          <t>Who was the youngest Prime Minister of India?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>First among equals</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Above all ministers</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Constitutional dictator</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Presiding officer</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>First among equals</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>The PM is the keystone of the cabinet system and is the senior-most.</t>
+          <t>He became PM at the age of 40.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which Prime Minister of India was not a member of Parliament at the time of appointment?</t>
+          <t>Which Article indirectly recognizes the existence of the Prime Minister without naming the post?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>He was appointed PM and later contested elections.</t>
+          <t>It mentions a Council of Ministers headed by the PM.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Prime Minister can be a member of which of the following?</t>
+          <t>What happens if the Prime Minister loses majority support in Lok Sabha?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Only Lok Sabha</t>
+          <t>Dismissed by President</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Only Rajya Sabha</t>
+          <t>Resigns</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Any House</t>
+          <t>Continues till term ends</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Only Legislative Assembly</t>
+          <t>Impeached</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Any House</t>
+          <t>Resigns</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PM can be from Lok Sabha or Rajya Sabha.</t>
+          <t>Losing majority means the PM must resign.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>In which year was the post of Deputy Prime Minister first created in India?</t>
+          <t>The Prime Minister is the ex-officio Chairman of which of the following?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>Planning Board</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>National Integration Council</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>National Integration Council</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sardar Vallabhbhai Patel was the first Deputy PM in 1947.</t>
+          <t>PM chairs this council promoting national unity.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which one of the following is not a function of the Prime Minister?</t>
+          <t>Which Prime Minister lost a motion of confidence but refused to resign, leading to a constitutional crisis?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Allocating portfolios</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Presiding over cabinet meetings</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dismissing ministers</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Advising President</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Dismissing ministers</t>
-        </is>
-      </c>
+          <t>Indira Gandhi</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Only the President can formally dismiss ministers on PM’s advice.</t>
+          <t>All PMs respected the no-confidence result and resigned accordingly.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>How long can a person remain Prime Minister without being a member of either House of Parliament?</t>
+          <t>Who served as PM after the assassination of Indira Gandhi?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Indefinitely</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>He/she must become a member within 6 months.</t>
+          <t>He was immediately sworn in after her assassination in 1984.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which committee is headed by the Prime Minister?</t>
+          <t>Which one of the following is not a function of the Prime Minister?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>Allocating portfolios</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Estimates Committee</t>
+          <t>Presiding over cabinet meetings</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Planning Commission</t>
+          <t>Dismissing ministers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>Advising President</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>Dismissing ministers</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>PM is the ex-officio Chairperson of NITI Aayog.</t>
+          <t>Only the President can formally dismiss ministers on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The term of office of the Prime Minister is</t>
+          <t>Who can ask the Prime Minister to prove majority in Lok Sabha?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Till President desires</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>As long as he/she has majority support</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>As long as he/she has majority support</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>There is no fixed term; it depends on majority in Lok Sabha.</t>
+          <t>If doubt arises, President can ask PM to prove majority.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Prime Minister acts as a link between</t>
+          <t>Who succeeded Lal Bahadur Shastri as Prime Minister?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>President and Parliament</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cabinet and Judiciary</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Parliament and States</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>President and Cabinet</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>President and Cabinet</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>PM communicates Cabinet decisions to the President.</t>
+          <t>She took over as PM in 1966 after Shastri’s death.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Who was India’s first non-Congress Prime Minister?</t>
+          <t>Which of the following statements is true about PM’s resignation?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>It must be accepted by President</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>It is effective immediately</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>It must be in writing</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>It is reviewed by Supreme Court</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>It must be accepted by President</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>He became PM in 1977 from the Janata Party.</t>
+          <t>Resignation becomes effective once accepted by the President.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Who is known as the 'Father of Indian Economic Reforms'?</t>
+          <t>Who among the following served as both Prime Minister and President of India?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>PV Narasimha Rao</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Manmohan Singh</t>
-        </is>
-      </c>
+          <t>V V Giri</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>As Finance Minister in 1991, he launched liberalization reforms.</t>
+          <t>No one has held both posts; they are distinct positions.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>What is the position of the Prime Minister in the Union Cabinet?</t>
+          <t>Which PM’s tenure saw the passage of the RTI Act?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Junior Minister</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Head of Cabinet</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nominal Head</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Head of Cabinet</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>The PM is the head and coordinates its functions.</t>
+          <t>Right to Information Act was passed in 2005.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which Article establishes the Council of Ministers with the Prime Minister at the head?</t>
+          <t>The resignation of the Prime Minister means the resignation of</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Only PM</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>PM and Vice President</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Entire Council of Ministers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Only Cabinet Ministers</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Entire Council of Ministers</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>It provides for a Council of Ministers headed by the PM to aid and advise the President.</t>
+          <t>Since the PM is head, his resignation dissolves the Council.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Prime Minister is responsible to which body?</t>
+          <t>The term of office of the Prime Minister is</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Till President desires</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>As long as he/she has majority support</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>As long as he/she has majority support</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>The PM is collectively responsible to the Lok Sabha.</t>
+          <t>There is no fixed term; it depends on majority in Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which of the following Prime Ministers never faced Parliament during their tenure?</t>
+          <t>What is the difference between Cabinet and Council of Ministers in context of PM’s role?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>No difference</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Cabinet is a part of CoM</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>PM heads Cabinet only</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Only Cabinet advises President</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Cabinet is a part of CoM</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>He was caretaker PM twice, without facing Parliament.</t>
+          <t>PM leads both, but Cabinet is an inner core of senior ministers.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Who succeeded Lal Bahadur Shastri as Prime Minister?</t>
+          <t>The Prime Minister’s advisory role to the President is</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Discretionary</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Ceremonial</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>She took over as PM in 1966 after Shastri’s death.</t>
+          <t>Under Article 74(1), advice of CoM led by PM is binding.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The resignation of the Prime Minister means the resignation of</t>
+          <t>Which Prime Minister had the shortest tenure?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Only PM</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PM and Vice President</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Entire Council of Ministers</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Only Cabinet Ministers</t>
+          <t>Atal Bihari Vajpayee (1996)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Entire Council of Ministers</t>
+          <t>Atal Bihari Vajpayee (1996)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Since the PM is head, his resignation dissolves the Council.</t>
+          <t>He served for just 13 days before resigning.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Who administers the oath of office to the Prime Minister?</t>
+          <t>Which PM faced criticism for Operation Blue Star?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>The President administers the oath of office and secrecy to the PM.</t>
+          <t>She ordered the military operation at the Golden Temple in 1984.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which of the following Prime Ministers served two non-consecutive terms?</t>
+          <t>Which Prime Minister was arrested during the British Quit India Movement?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1526,12 +1510,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1541,172 +1525,172 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>He served briefly in 1996 and then from 1998 to 2004.</t>
+          <t>He was imprisoned multiple times during the freedom movement.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Prime Minister is the ex-officio Chairman of which of the following?</t>
+          <t>Under Article 75(3), the Council of Ministers is collectively responsible to which House?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Planning Board</t>
+          <t>Both Houses</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>National Integration Council</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>National Integration Council</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>PM chairs this council promoting national unity.</t>
+          <t>This ensures accountability of executive to the lower house.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Who advises the President on the appointment of other ministers?</t>
+          <t>If a Prime Minister is convicted in a criminal case and sentenced for more than 2 years, what happens?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Can continue</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Disqualified immediately</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>President decides</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cabinet Secretary</t>
+          <t>Can appeal to remain</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Disqualified immediately</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>President appoints ministers on advice of the PM.</t>
+          <t>As per RPA 1951 and SC rulings, such a person loses membership and hence PMship.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which Prime Minister gave the slogan 'Garibi Hatao'?</t>
+          <t>Which PM was in power during Pokhran-II nuclear tests in 1998?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>Manmohan Singh</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Atal Bihari Vajpayee</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>P V Narasimha Rao</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>Rajiv Gandhi</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Lal Bahadur Shastri</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Indira Gandhi</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Jawaharlal Nehru</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>She gave this slogan during the 1971 election campaign.</t>
+          <t>He ordered the nuclear tests shortly after becoming PM.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Who can ask the Prime Minister to prove majority in Lok Sabha?</t>
+          <t>Who has the final authority to decide on the portfolios of Union Ministers?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Cabinet Secretary</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Cabinet Committee</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>If doubt arises, President can ask PM to prove majority.</t>
+          <t>The PM allocates portfolios and can reshuffle them at will.</t>
         </is>
       </c>
     </row>
@@ -1752,2721 +1736,2717 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Prime Minister can be removed by</t>
+          <t>When does the Prime Minister tender resignation?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>After term completion</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>After President’s directive</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Impeachment</t>
+          <t>After defeat in election</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lok Sabha via no-confidence motion</t>
+          <t>After losing Lok Sabha majority</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lok Sabha via no-confidence motion</t>
+          <t>After losing Lok Sabha majority</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>A successful no-confidence motion removes the PM.</t>
+          <t>If PM loses support, he must resign.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Prime Minister’s Office (PMO) is</t>
+          <t>How many times has the office of Prime Minister been held by someone from Rajya Sabha?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Statutory body</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Constitutional body</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Extra-constitutional body</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Judicial body</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Extra-constitutional body</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>The PMO is not mentioned in the Constitution but exists in practice.</t>
+          <t>Indira Gandhi, HD Deve Gowda, and Manmohan Singh have served while being Rajya Sabha members.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Who was the first female Prime Minister of India?</t>
+          <t>Which Article establishes the Council of Ministers with the Prime Minister at the head?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sushma Swaraj</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Meira Kumar</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>She became PM in 1966.</t>
+          <t>It provides for a Council of Ministers headed by the PM to aid and advise the President.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which Prime Minister implemented the Green Revolution policies?</t>
+          <t>Which Prime Minister nationalized 14 major banks in India?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>Morarji Desai</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>P V Narasimha Rao</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Rajiv Gandhi</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Indira Gandhi</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Green Revolution was accelerated during her tenure.</t>
+          <t>This was done in 1969 as part of socialist economic reforms.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Who was the youngest Prime Minister of India?</t>
+          <t>Which constitutional article allows the PM to recommend President's Rule in a state?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Article 365</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>He became PM at the age of 40.</t>
+          <t>It allows the President to impose President’s Rule based on Governor’s or PM’s recommendation.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which Prime Minister signed the Simla Agreement in 1972?</t>
+          <t>What is the tenure of Prime Minister of India?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Fixed 5 years</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Fixed 6 years</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Depends on President</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>No fixed tenure</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>No fixed tenure</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>It was signed with Pakistan after the 1971 war.</t>
+          <t>PM holds office during the pleasure of the President, as long as majority is maintained.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Prime Minister is the leader of which house by convention?</t>
+          <t>Which PM's government passed the 73rd and 74th Constitutional Amendments?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Council of States</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Upper House</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Although not mandatory, the PM usually leads the Lok Sabha.</t>
+          <t>These Acts gave constitutional status to Panchayati Raj and municipalities.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>When does the Prime Minister tender resignation?</t>
+          <t>The Prime Minister can be a member of which of the following?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>After term completion</t>
+          <t>Only Lok Sabha</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>After President’s directive</t>
+          <t>Only Rajya Sabha</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>After defeat in election</t>
+          <t>Any House</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>After losing Lok Sabha majority</t>
+          <t>Only Legislative Assembly</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>After losing Lok Sabha majority</t>
+          <t>Any House</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>If PM loses support, he must resign.</t>
+          <t>PM can be from Lok Sabha or Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What is the tenure of Prime Minister of India?</t>
+          <t>Who was the first Prime Minister to lose a confidence vote in Lok Sabha?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fixed 5 years</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Fixed 6 years</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Depends on President</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>No fixed tenure</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>No fixed tenure</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>PM holds office during the pleasure of the President, as long as majority is maintained.</t>
+          <t>He lost majority in 1979 and resigned before facing a vote.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which Prime Minister was a recipient of Bharat Ratna before becoming PM?</t>
+          <t>Who was the first female Prime Minister of India?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>Sushma Swaraj</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Morarji Desai</t>
-        </is>
-      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Meira Kumar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>He received Bharat Ratna in 1991, after retirement.</t>
+          <t>She became PM in 1966.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Can a person from outside Parliament be appointed as PM?</t>
+          <t>If the Prime Minister dies suddenly, who becomes the Acting PM?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Yes, for 3 months</t>
+          <t>Senior-most Cabinet Minister</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Yes, for 6 months</t>
+          <t>Home Minister</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Only if nominated</t>
+          <t>No provision</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Yes, for 6 months</t>
+          <t>Senior-most Cabinet Minister</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>He/she must get elected to Parliament within 6 months.</t>
+          <t>Conventionally, the senior-most is asked to act until a new leader is chosen.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Who served as PM after the assassination of Indira Gandhi?</t>
+          <t>Which PM led the Janata Dal government formed after the Mandal Commission recommendations?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>Charan Singh</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>HD Deve Gowda</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>VP Singh</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Morarji Desai</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Rajiv Gandhi</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>IK Gujral</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>He was immediately sworn in after her assassination in 1984.</t>
+          <t>He implemented the Mandal Commission recommendations in 1990.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which Prime Minister initiated the 'Look East Policy'?</t>
+          <t>Which PM was referred to as the 'Chanakya of Indian Politics'?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PV Narasimha Rao</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>PV Narasimha Rao</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>He initiated the policy to strengthen relations with Southeast Asia.</t>
+          <t>Known for his political strategies and handling of minority government.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which Prime Minister was also a Reserve Bank Governor?</t>
+          <t>What is the minimum educational qualification required to become Prime Minister in India?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Graduate</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>12th pass</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>No formal qualification</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Postgraduate</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>No formal qualification</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>He served as RBI Governor from 1982–1985.</t>
+          <t>The Constitution doesn’t prescribe any educational qualification.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which Prime Minister had the shortest tenure?</t>
+          <t>In which year was the post of Deputy Prime Minister first created in India?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee (1996)</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee (1996)</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>He served for just 13 days before resigning.</t>
+          <t>Sardar Vallabhbhai Patel was the first Deputy PM in 1947.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which of these Prime Ministers was never a Member of Lok Sabha?</t>
+          <t>Which Prime Minister was in office during the Kargil War?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>Atal Bihari Vajpayee</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>P V Narasimha Rao</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>Manmohan Singh</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Narendra Modi</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Morarji Desai</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>He was a member of Rajya Sabha during his PM tenure.</t>
+          <t>The Kargil conflict occurred in 1999 during his tenure.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who among the following served as both Prime Minister and President of India?</t>
+          <t>Which Schedule of the Indian Constitution is indirectly related to the responsibilities of the Prime Minister?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>2nd Schedule</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>3rd Schedule</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>V V Giri</t>
+          <t>7th Schedule</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>3rd Schedule</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>No one has held both posts; they are distinct positions.</t>
+          <t>It contains the oath of office and secrecy taken by the PM and other ministers.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>In the case of death or resignation of Prime Minister, who appoints the new PM?</t>
+          <t>Which Prime Minister initiated the 'Look East Policy'?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>PV Narasimha Rao</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>PV Narasimha Rao</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>The President appoints the new Prime Minister based on majority support.</t>
+          <t>He initiated the policy to strengthen relations with Southeast Asia.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Under which circumstances can the Prime Minister recommend dissolution of Lok Sabha to the President?</t>
+          <t>How long can a person remain Prime Minister without being a member of either House of Parliament?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Only after a confidence vote</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Only with Cabinet approval</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Only after consulting Speaker</t>
+          <t>Indefinitely</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>The PM can advise dissolution anytime, subject to constitutional propriety.</t>
+          <t>He/she must become a member within 6 months.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>In which landmark case did the Supreme Court observe that the Prime Minister is the "chief spokesman of the government"?</t>
+          <t>Which PM was awarded the Bharat Ratna posthumously in 1991?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>S.P. Gupta case</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Keshavananda Bharati case</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Shamsher Singh case</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SR Bommai case</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Shamsher Singh case</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>This case clarified the role of PM in the cabinet system under parliamentary democracy.</t>
+          <t>He was assassinated in 1991 and awarded the Bharat Ratna posthumously.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Who has the final authority to decide on the portfolios of Union Ministers?</t>
+          <t>Which of the following committees is headed by the PM and deals with internal security?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Political Affairs Committee</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Appointments Committee</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cabinet Secretary</t>
+          <t>Security Committee</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cabinet Committee</t>
+          <t>Cabinet Committee on Security</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Cabinet Committee on Security</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>The PM allocates portfolios and can reshuffle them at will.</t>
+          <t>This committee deals with defense and internal security issues.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which Schedule of the Indian Constitution is indirectly related to the responsibilities of the Prime Minister?</t>
+          <t>Which Article empowers the President to act in accordance with the advice of the Council of Ministers headed by PM?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2nd Schedule</t>
+          <t>Article 74(1)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3rd Schedule</t>
+          <t>Article 75(3)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>7th Schedule</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>Article 78</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3rd Schedule</t>
+          <t>Article 74(1)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>It contains the oath of office and secrecy taken by the PM and other ministers.</t>
+          <t>After the 42nd and 44th Amendments, the President is bound by the CoM's advice.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>If the Prime Minister is a member of Rajya Sabha, which of the following is true?</t>
+          <t>The Prime Minister can be removed by</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cannot take part in debates</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cannot vote in Lok Sabha</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cannot be PM</t>
+          <t>Impeachment</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Must resign from Rajya Sabha</t>
+          <t>Lok Sabha via no-confidence motion</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cannot vote in Lok Sabha</t>
+          <t>Lok Sabha via no-confidence motion</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>A Rajya Sabha MP can participate but not vote in Lok Sabha.</t>
+          <t>A successful no-confidence motion removes the PM.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Prime Minister is not mentioned by name in which part of the Constitution?</t>
+          <t>Under which constitutional amendment is the advice of the Council of Ministers to the President made binding?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Part V</t>
+          <t>38th Amendment</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Part VI</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fundamental Rights make no mention of the PM; it is dealt with in Part V (Union).</t>
+          <t>The 42nd Amendment (1976) made Presidential advice binding.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which Article empowers the President to act in accordance with the advice of the Council of Ministers headed by PM?</t>
+          <t>What is the significance of the expression "pleasure of the President" in context of PM's tenure?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Article 74(1)</t>
+          <t>Symbolic</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Article 75(3)</t>
+          <t>President can remove at will</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>PM can be dismissed anytime</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Article 78</t>
+          <t>Depends on Lok Sabha majority</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Article 74(1)</t>
+          <t>Depends on Lok Sabha majority</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>After the 42nd and 44th Amendments, the President is bound by the CoM's advice.</t>
+          <t>Though appointed by President, PM must enjoy majority support in Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which Prime Minister lost a motion of confidence but refused to resign, leading to a constitutional crisis?</t>
+          <t>Which of the following is a discretionary power of the President regarding the Prime Minister?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Dismissal</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Appointment when no party has majority</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Salary fixation</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Policy review</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Appointment when no party has majority</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>All PMs respected the no-confidence result and resigned accordingly.</t>
+          <t>In case of no clear majority, President has discretion in appointing the PM.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which PM was heading a coalition but completed a full 5-year term for the first time?</t>
+          <t>Which Prime Minister set up the Sarkaria Commission on Centre-State relations?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>IK Gujral</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>He led the NDA government from 1999–2004 successfully.</t>
+          <t>The commission was set up in 1983 during his tenure.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which of the following is **not** a Cabinet Committee chaired by the Prime Minister?</t>
+          <t>The Prime Minister is the head of which body?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Appointments Committee</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Political Affairs Committee</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Economic Affairs Committee</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Parliamentary Standing Committee</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parliamentary Standing Committee</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>These are headed by MPs or Speaker, not PM.</t>
+          <t>The PM is the head of the Council of Ministers and leads the executive branch.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Under Article 75(3), the Council of Ministers is collectively responsible to which House?</t>
+          <t>Which Prime Minister's term saw the introduction of MGNREGA?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Both Houses</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>This ensures accountability of executive to the lower house.</t>
+          <t>MGNREGA was launched in 2006 under his leadership.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>If a Prime Minister is convicted in a criminal case and sentenced for more than 2 years, what happens?</t>
+          <t>What is the position of the Prime Minister in the Union Cabinet?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Can continue</t>
+          <t>Junior Minister</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Disqualified immediately</t>
+          <t>Head of Cabinet</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>President decides</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Can appeal to remain</t>
-        </is>
-      </c>
+          <t>Nominal Head</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Disqualified immediately</t>
+          <t>Head of Cabinet</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>As per RPA 1951 and SC rulings, such a person loses membership and hence PMship.</t>
+          <t>The PM is the head and coordinates its functions.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The PM acts as a channel of communication between the President and</t>
+          <t>Which Prime Minister’s government fell due to the withdrawal of support by AIADMK in 1999?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>IK Gujral</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>PM is the link between President and CoM as per Article 78.</t>
+          <t>His government fell by one vote in 1999 after AIADMK withdrew support.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which Article indirectly recognizes the existence of the Prime Minister without naming the post?</t>
+          <t>In which landmark case did the Supreme Court observe that the Prime Minister is the "chief spokesman of the government"?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>S.P. Gupta case</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Keshavananda Bharati case</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>Shamsher Singh case</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>SR Bommai case</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Shamsher Singh case</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>It mentions a Council of Ministers headed by the PM.</t>
+          <t>This case clarified the role of PM in the cabinet system under parliamentary democracy.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which of the following events did **not** require the PM to face a no-confidence motion?</t>
+          <t>Which of these Prime Ministers was never a Member of Lok Sabha?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Emergency of 1975</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Demolition of Babri Masjid</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kargil War</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Indira Gandhi’s election verdict</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Demolition of Babri Masjid</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Though controversial, the PM wasn’t asked to prove majority immediately after it.</t>
+          <t>He was a member of Rajya Sabha during his PM tenure.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>How many times has the office of Prime Minister been held by someone from Rajya Sabha?</t>
+          <t>The Prime Minister’s Office (PMO) is</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Statutory body</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Constitutional body</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Extra-constitutional body</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Judicial body</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Extra-constitutional body</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Indira Gandhi, HD Deve Gowda, and Manmohan Singh have served while being Rajya Sabha members.</t>
+          <t>The PMO is not mentioned in the Constitution but exists in practice.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which Prime Minister launched the 20-Point Programme in 1975?</t>
+          <t>Which Prime Minister was a recipient of Bharat Ratna before becoming PM?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>Indira Gandhi</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Morarji Desai</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>Rajiv Gandhi</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Atal Bihari Vajpayee</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Indira Gandhi</t>
-        </is>
-      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>It was a socio-economic initiative launched during the Emergency.</t>
+          <t>He received Bharat Ratna in 1991, after retirement.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister to lose a confidence vote in Lok Sabha?</t>
+          <t>Which of the following events did **not** require the PM to face a no-confidence motion?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Emergency of 1975</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Demolition of Babri Masjid</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Kargil War</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Indira Gandhi’s election verdict</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Demolition of Babri Masjid</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>He lost majority in 1979 and resigned before facing a vote.</t>
+          <t>Though controversial, the PM wasn’t asked to prove majority immediately after it.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which PM passed away while in office outside India?</t>
+          <t>The PM acts as a channel of communication between the President and</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>He died in Tashkent (USSR) after signing the Tashkent Agreement in 1966.</t>
+          <t>PM is the link between President and CoM as per Article 78.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Prime Minister’s advisory role to the President is</t>
+          <t>Which Prime Minister implemented the Green Revolution policies?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Discretionary</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ceremonial</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Under Article 74(1), advice of CoM led by PM is binding.</t>
+          <t>Green Revolution was accelerated during her tenure.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What is the significance of the expression "pleasure of the President" in context of PM's tenure?</t>
+          <t>Which PM is associated with the Golden Quadrilateral highway project?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Symbolic</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>President can remove at will</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PM can be dismissed anytime</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Depends on Lok Sabha majority</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Depends on Lok Sabha majority</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Though appointed by President, PM must enjoy majority support in Lok Sabha.</t>
+          <t>The project was launched during his tenure as part of NHDP.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>If the Prime Minister dies suddenly, who becomes the Acting PM?</t>
+          <t>Which Prime Minister had the shortest time between assuming office and facing a no-confidence motion?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Senior-most Cabinet Minister</t>
+          <t>Atal Bihari Vajpayee (1996)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Home Minister</t>
+          <t>IK Gujral</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>No provision</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Senior-most Cabinet Minister</t>
+          <t>Atal Bihari Vajpayee (1996)</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Conventionally, the senior-most is asked to act until a new leader is chosen.</t>
+          <t>He faced and lost a no-confidence vote within 13 days.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which Prime Minister abolished the Privy Purses of former princely rulers?</t>
+          <t>The Prime Minister is described as which of the following?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>First among equals</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Above all ministers</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Constitutional dictator</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Presiding officer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>First among equals</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>The move was made via a Constitutional Amendment in 1971.</t>
+          <t>The PM is the keystone of the cabinet system and is the senior-most.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What is the difference between Cabinet and Council of Ministers in context of PM’s role?</t>
+          <t>If the Prime Minister is a member of Rajya Sabha, which of the following is true?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>No difference</t>
+          <t>Cannot take part in debates</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cabinet is a part of CoM</t>
+          <t>Cannot vote in Lok Sabha</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PM heads Cabinet only</t>
+          <t>Cannot be PM</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Only Cabinet advises President</t>
+          <t>Must resign from Rajya Sabha</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cabinet is a part of CoM</t>
+          <t>Cannot vote in Lok Sabha</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>PM leads both, but Cabinet is an inner core of senior ministers.</t>
+          <t>A Rajya Sabha MP can participate but not vote in Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which PM led the Janata Dal government formed after the Mandal Commission recommendations?</t>
+          <t>Which Prime Minister signed the Simla Agreement in 1972?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>IK Gujral</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>He implemented the Mandal Commission recommendations in 1990.</t>
+          <t>It was signed with Pakistan after the 1971 war.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which Prime Minister was in office when the Anti-Defection Law was passed?</t>
+          <t>Who advises the President on the appointment of other ministers?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Cabinet Secretary</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>The 52nd Amendment Act, 1985 was passed during Rajiv Gandhi's tenure.</t>
+          <t>President appoints ministers on advice of the PM.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Under which constitutional amendment is the advice of the Council of Ministers to the President made binding?</t>
+          <t>Which Prime Minister of India was not a member of Parliament at the time of appointment?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>38th Amendment</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>The 42nd Amendment (1976) made Presidential advice binding.</t>
+          <t>He was appointed PM and later contested elections.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which Prime Minister had the shortest time between assuming office and facing a no-confidence motion?</t>
+          <t>Which Article of the Constitution deals with the Prime Minister?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee (1996)</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IK Gujral</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Article 78</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee (1996)</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>He faced and lost a no-confidence vote within 13 days.</t>
+          <t>Article 75 provides for the appointment of the Prime Minister and other ministers.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which Prime Minister was arrested during the British Quit India Movement?</t>
+          <t>The Prime Minister must be a member of which House?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Only Lok Sabha</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>He was imprisoned multiple times during the freedom movement.</t>
+          <t>The PM can be a member of either Lok Sabha or Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>What is the minimum educational qualification required to become Prime Minister in India?</t>
+          <t>Who acted as Prime Minister in between Jawaharlal Nehru's death and Lal Bahadur Shastri's appointment?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Graduate</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>12th pass</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>No formal qualification</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Postgraduate</t>
+          <t>K Kamaraj</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>No formal qualification</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>The Constitution doesn’t prescribe any educational qualification.</t>
+          <t>He served as interim PM after Nehru's death in 1964.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which Prime Minister nationalized 14 major banks in India?</t>
+          <t>Who administers the oath of office to the Prime Minister?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>This was done in 1969 as part of socialist economic reforms.</t>
+          <t>The President administers the oath of office and secrecy to the PM.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which Prime Minister initiated the policy of Economic Liberalization in India?</t>
+          <t>Under which circumstances can the Prime Minister recommend dissolution of Lok Sabha to the President?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Any time</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Only after a confidence vote</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Only with Cabinet approval</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Only after consulting Speaker</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Any time</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>His government started reforms in 1991 with Manmohan Singh as Finance Minister.</t>
+          <t>The PM can advise dissolution anytime, subject to constitutional propriety.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which Prime Minister’s government fell due to the withdrawal of support by AIADMK in 1999?</t>
+          <t>Which Prime Minister was also a Reserve Bank Governor?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IK Gujral</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>Indira Gandhi</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Lal Bahadur Shastri</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
           <t>Manmohan Singh</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>HD Deve Gowda</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Atal Bihari Vajpayee</t>
-        </is>
-      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>His government fell by one vote in 1999 after AIADMK withdrew support.</t>
+          <t>He served as RBI Governor from 1982–1985.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which Prime Minister faced the most number of no-confidence motions?</t>
+          <t>The Prime Minister is the leader of which house by convention?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Council of States</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Upper House</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>She faced the most no-confidence motions during her tenure.</t>
+          <t>Although not mandatory, the PM usually leads the Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which of the following statements is true about PM’s resignation?</t>
+          <t>Can a person from outside Parliament be appointed as PM?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>It must be accepted by President</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>It is effective immediately</t>
+          <t>Yes, for 3 months</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>It must be in writing</t>
+          <t>Yes, for 6 months</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>It is reviewed by Supreme Court</t>
+          <t>Only if nominated</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>It must be accepted by President</t>
+          <t>Yes, for 6 months</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Resignation becomes effective once accepted by the President.</t>
+          <t>He/she must get elected to Parliament within 6 months.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Who acted as Prime Minister in between Jawaharlal Nehru's death and Lal Bahadur Shastri's appointment?</t>
+          <t>The Prime Minister is not mentioned by name in which part of the Constitution?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Part V</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Part VI</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>K Kamaraj</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>He served as interim PM after Nehru's death in 1964.</t>
+          <t>Fundamental Rights make no mention of the PM; it is dealt with in Part V (Union).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which Prime Minister set up the Sarkaria Commission on Centre-State relations?</t>
+          <t>The Prime Minister communicates to the President all decisions of the Council of Ministers under which Article?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Article 78</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Article 78</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>The commission was set up in 1983 during his tenure.</t>
+          <t>It is the duty of the PM to inform the President of all cabinet decisions.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which constitutional article allows the PM to recommend President's Rule in a state?</t>
+          <t>Which Prime Minister was in office when the Anti-Defection Law was passed?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Article 365</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>It allows the President to impose President’s Rule based on Governor’s or PM’s recommendation.</t>
+          <t>The 52nd Amendment Act, 1985 was passed during Rajiv Gandhi's tenure.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which PM was in power during Pokhran-II nuclear tests in 1998?</t>
+          <t>Which Prime Minister had the longest uninterrupted tenure?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
+          <t>Indira Gandhi</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Rajiv Gandhi</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Jawaharlal Nehru</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>Manmohan Singh</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Atal Bihari Vajpayee</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>P V Narasimha Rao</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Rajiv Gandhi</t>
-        </is>
-      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>He ordered the nuclear tests shortly after becoming PM.</t>
+          <t>He served continuously for 17 years from 1947 to 1964.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which PM was referred to as the 'Chanakya of Indian Politics'?</t>
+          <t>The Prime Minister is responsible to which body?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Known for his political strategies and handling of minority government.</t>
+          <t>The PM is collectively responsible to the Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which Prime Minister's term saw the introduction of MGNREGA?</t>
+          <t>Which of the following Prime Ministers never faced Parliament during their tenure?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>MGNREGA was launched in 2006 under his leadership.</t>
+          <t>He was caretaker PM twice, without facing Parliament.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which PM’s tenure saw the passage of the RTI Act?</t>
+          <t>Which committee is headed by the Prime Minister?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Estimates Committee</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Planning Commission</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Right to Information Act was passed in 2005.</t>
+          <t>PM is the ex-officio Chairperson of NITI Aayog.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which PM was awarded the Bharat Ratna posthumously in 1991?</t>
+          <t>Which Prime Minister abolished the Privy Purses of former princely rulers?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
+          <t>Lal Bahadur Shastri</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jawaharlal Nehru</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Indira Gandhi</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t>Rajiv Gandhi</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Lal Bahadur Shastri</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Jawaharlal Nehru</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Rajiv Gandhi</t>
-        </is>
-      </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>He was assassinated in 1991 and awarded the Bharat Ratna posthumously.</t>
+          <t>The move was made via a Constitutional Amendment in 1971.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which of the following committees is headed by the PM and deals with internal security?</t>
+          <t>Which PM was heading a coalition but completed a full 5-year term for the first time?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Political Affairs Committee</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Appointments Committee</t>
+          <t>IK Gujral</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Security Committee</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cabinet Committee on Security</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cabinet Committee on Security</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>This committee deals with defense and internal security issues.</t>
+          <t>He led the NDA government from 1999–2004 successfully.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which PM is associated with the Golden Quadrilateral highway project?</t>
+          <t>The Prime Minister acts as a link between</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>President and Parliament</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Cabinet and Judiciary</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Parliament and States</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>President and Cabinet</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>President and Cabinet</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>The project was launched during his tenure as part of NHDP.</t>
+          <t>PM communicates Cabinet decisions to the President.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which Prime Minister had the longest uninterrupted tenure?</t>
+          <t>Who is known as the 'Father of Indian Economic Reforms'?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
+          <t>Atal Bihari Vajpayee</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Rajiv Gandhi</t>
-        </is>
-      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
+          <t>PV Narasimha Rao</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
           <t>Manmohan Singh</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Jawaharlal Nehru</t>
-        </is>
-      </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>He served continuously for 17 years from 1947 to 1964.</t>
+          <t>As Finance Minister in 1991, he launched liberalization reforms.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which PM faced criticism for Operation Blue Star?</t>
+          <t>Which Prime Minister initiated the policy of Economic Liberalization in India?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>She ordered the military operation at the Golden Temple in 1984.</t>
+          <t>His government started reforms in 1991 with Manmohan Singh as Finance Minister.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which PM's government passed the 73rd and 74th Constitutional Amendments?</t>
+          <t>Which of the following is **not** a Cabinet Committee chaired by the Prime Minister?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Appointments Committee</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Political Affairs Committee</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Economic Affairs Committee</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Parliamentary Standing Committee</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Parliamentary Standing Committee</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>These Acts gave constitutional status to Panchayati Raj and municipalities.</t>
+          <t>These are headed by MPs or Speaker, not PM.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which Prime Minister introduced the slogan 'Minimum Government, Maximum Governance'?</t>
+          <t>Which of the following Prime Ministers served two non-consecutive terms?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t>Atal Bihari Vajpayee</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Narendra Modi</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>Manmohan Singh</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Narendra Modi</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Narendra Modi</t>
-        </is>
-      </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>It was part of his 2014 election campaign vision.</t>
+          <t>He served briefly in 1996 and then from 1998 to 2004.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which Prime Minister was in office during the Kargil War?</t>
+          <t>Who was India’s first non-Congress Prime Minister?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>The Kargil conflict occurred in 1999 during his tenure.</t>
+          <t>He became PM in 1977 from the Janata Party.</t>
         </is>
       </c>
     </row>

--- a/Data/IPPrimeminister.xlsx
+++ b/Data/IPPrimeminister.xlsx
@@ -472,51 +472,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which Prime Minister introduced the slogan 'Minimum Government, Maximum Governance'?</t>
+          <t>Which Article indirectly recognizes the existence of the Prime Minister without naming the post?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>It was part of his 2014 election campaign vision.</t>
+          <t>It mentions a Council of Ministers headed by the PM.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which Prime Minister faced the most number of no-confidence motions?</t>
+          <t>Who was the youngest Prime Minister of India?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -526,277 +526,277 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Narendra Modi</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Morarji Desai</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Rajiv Gandhi</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Atal Bihari Vajpayee</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Indira Gandhi</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>She faced the most no-confidence motions during her tenure.</t>
+          <t>He became PM at the age of 40.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>In the case of death or resignation of Prime Minister, who appoints the new PM?</t>
+          <t>Which Prime Minister gave the slogan 'Garibi Hatao'?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>The President appoints the new Prime Minister based on majority support.</t>
+          <t>She gave this slogan during the 1971 election campaign.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which Prime Minister launched the 20-Point Programme in 1975?</t>
+          <t>Who appoints the Prime Minister of India?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>It was a socio-economic initiative launched during the Emergency.</t>
+          <t>The President formally appoints the PM, usually the leader of the majority in Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Who presides over the meetings of the Union Council of Ministers?</t>
+          <t>Which PM passed away while in office outside India?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>The PM is the head of the Council and chairs its meetings.</t>
+          <t>He died in Tashkent (USSR) after signing the Tashkent Agreement in 1966.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which PM passed away while in office outside India?</t>
+          <t>Who presides over the meetings of the Union Council of Ministers?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>He died in Tashkent (USSR) after signing the Tashkent Agreement in 1966.</t>
+          <t>The PM is the head of the Council and chairs its meetings.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Who appoints the Prime Minister of India?</t>
+          <t>Which Prime Minister launched the 20-Point Programme in 1975?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>The President formally appoints the PM, usually the leader of the majority in Lok Sabha.</t>
+          <t>It was a socio-economic initiative launched during the Emergency.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which Prime Minister gave the slogan 'Garibi Hatao'?</t>
+          <t>In the case of death or resignation of Prime Minister, who appoints the new PM?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>She gave this slogan during the 1971 election campaign.</t>
+          <t>The President appoints the new Prime Minister based on majority support.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Who was the youngest Prime Minister of India?</t>
+          <t>Which Prime Minister faced the most number of no-confidence motions?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -806,194 +806,194 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Jawaharlal Nehru</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Rajiv Gandhi</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Narendra Modi</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>He became PM at the age of 40.</t>
+          <t>She faced the most no-confidence motions during her tenure.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which Article indirectly recognizes the existence of the Prime Minister without naming the post?</t>
+          <t>Which Prime Minister introduced the slogan 'Minimum Government, Maximum Governance'?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>It mentions a Council of Ministers headed by the PM.</t>
+          <t>It was part of his 2014 election campaign vision.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>What happens if the Prime Minister loses majority support in Lok Sabha?</t>
+          <t>Which PM’s tenure saw the passage of the RTI Act?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dismissed by President</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Resigns</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Continues till term ends</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Impeached</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Resigns</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Losing majority means the PM must resign.</t>
+          <t>Right to Information Act was passed in 2005.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Prime Minister is the ex-officio Chairman of which of the following?</t>
+          <t>Who among the following served as both Prime Minister and President of India?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Planning Board</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>National Integration Council</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>National Integration Council</t>
-        </is>
-      </c>
+          <t>V V Giri</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PM chairs this council promoting national unity.</t>
+          <t>No one has held both posts; they are distinct positions.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which Prime Minister lost a motion of confidence but refused to resign, leading to a constitutional crisis?</t>
+          <t>Which of the following statements is true about PM’s resignation?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>It must be accepted by President</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>It is effective immediately</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+          <t>It must be in writing</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>It is reviewed by Supreme Court</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>It must be accepted by President</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>All PMs respected the no-confidence result and resigned accordingly.</t>
+          <t>Resignation becomes effective once accepted by the President.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Who served as PM after the assassination of Indira Gandhi?</t>
+          <t>Who succeeded Lal Bahadur Shastri as Prime Minister?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1003,117 +1003,117 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>He was immediately sworn in after her assassination in 1984.</t>
+          <t>She took over as PM in 1966 after Shastri’s death.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which one of the following is not a function of the Prime Minister?</t>
+          <t>Who can ask the Prime Minister to prove majority in Lok Sabha?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Allocating portfolios</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Presiding over cabinet meetings</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dismissing ministers</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Advising President</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dismissing ministers</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Only the President can formally dismiss ministers on PM’s advice.</t>
+          <t>If doubt arises, President can ask PM to prove majority.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Who can ask the Prime Minister to prove majority in Lok Sabha?</t>
+          <t>Which one of the following is not a function of the Prime Minister?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Allocating portfolios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Presiding over cabinet meetings</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Dismissing ministers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Advising President</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Dismissing ministers</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>If doubt arises, President can ask PM to prove majority.</t>
+          <t>Only the President can formally dismiss ministers on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Who succeeded Lal Bahadur Shastri as Prime Minister?</t>
+          <t>Who served as PM after the assassination of Indira Gandhi?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1123,1404 +1123,1404 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Rajiv Gandhi</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Gulzarilal Nanda</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Charan Singh</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>She took over as PM in 1966 after Shastri’s death.</t>
+          <t>He was immediately sworn in after her assassination in 1984.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which of the following statements is true about PM’s resignation?</t>
+          <t>Which Prime Minister lost a motion of confidence but refused to resign, leading to a constitutional crisis?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>It must be accepted by President</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>It is effective immediately</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>It must be in writing</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>It is reviewed by Supreme Court</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>It must be accepted by President</t>
-        </is>
-      </c>
+          <t>Indira Gandhi</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Resignation becomes effective once accepted by the President.</t>
+          <t>All PMs respected the no-confidence result and resigned accordingly.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Who among the following served as both Prime Minister and President of India?</t>
+          <t>The Prime Minister is the ex-officio Chairman of which of the following?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>V V Giri</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+          <t>Planning Board</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>National Integration Council</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>National Integration Council</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No one has held both posts; they are distinct positions.</t>
+          <t>PM chairs this council promoting national unity.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which PM’s tenure saw the passage of the RTI Act?</t>
+          <t>What happens if the Prime Minister loses majority support in Lok Sabha?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Dismissed by President</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Resigns</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Continues till term ends</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Impeached</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Resigns</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Right to Information Act was passed in 2005.</t>
+          <t>Losing majority means the PM must resign.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The resignation of the Prime Minister means the resignation of</t>
+          <t>Which PM was in power during Pokhran-II nuclear tests in 1998?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Only PM</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PM and Vice President</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Entire Council of Ministers</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Only Cabinet Ministers</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Entire Council of Ministers</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Since the PM is head, his resignation dissolves the Council.</t>
+          <t>He ordered the nuclear tests shortly after becoming PM.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The term of office of the Prime Minister is</t>
+          <t>If a Prime Minister is convicted in a criminal case and sentenced for more than 2 years, what happens?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Can continue</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Disqualified immediately</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Till President desires</t>
+          <t>President decides</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>As long as he/she has majority support</t>
+          <t>Can appeal to remain</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>As long as he/she has majority support</t>
+          <t>Disqualified immediately</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>There is no fixed term; it depends on majority in Lok Sabha.</t>
+          <t>As per RPA 1951 and SC rulings, such a person loses membership and hence PMship.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What is the difference between Cabinet and Council of Ministers in context of PM’s role?</t>
+          <t>Under Article 75(3), the Council of Ministers is collectively responsible to which House?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No difference</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cabinet is a part of CoM</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PM heads Cabinet only</t>
+          <t>Both Houses</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Only Cabinet advises President</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cabinet is a part of CoM</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PM leads both, but Cabinet is an inner core of senior ministers.</t>
+          <t>This ensures accountability of executive to the lower house.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Prime Minister’s advisory role to the President is</t>
+          <t>Which Prime Minister was arrested during the British Quit India Movement?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Discretionary</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ceremonial</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Under Article 74(1), advice of CoM led by PM is binding.</t>
+          <t>He was imprisoned multiple times during the freedom movement.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which Prime Minister had the shortest tenure?</t>
+          <t>Which PM faced criticism for Operation Blue Star?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee (1996)</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee (1996)</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>He served for just 13 days before resigning.</t>
+          <t>She ordered the military operation at the Golden Temple in 1984.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which PM faced criticism for Operation Blue Star?</t>
+          <t>Which Prime Minister had the shortest tenure?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Atal Bihari Vajpayee (1996)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Atal Bihari Vajpayee (1996)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>She ordered the military operation at the Golden Temple in 1984.</t>
+          <t>He served for just 13 days before resigning.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which Prime Minister was arrested during the British Quit India Movement?</t>
+          <t>The Prime Minister’s advisory role to the President is</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Discretionary</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Ceremonial</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>He was imprisoned multiple times during the freedom movement.</t>
+          <t>Under Article 74(1), advice of CoM led by PM is binding.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Under Article 75(3), the Council of Ministers is collectively responsible to which House?</t>
+          <t>What is the difference between Cabinet and Council of Ministers in context of PM’s role?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>No difference</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Cabinet is a part of CoM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Both Houses</t>
+          <t>PM heads Cabinet only</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Only Cabinet advises President</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Cabinet is a part of CoM</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>This ensures accountability of executive to the lower house.</t>
+          <t>PM leads both, but Cabinet is an inner core of senior ministers.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>If a Prime Minister is convicted in a criminal case and sentenced for more than 2 years, what happens?</t>
+          <t>The term of office of the Prime Minister is</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Can continue</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Disqualified immediately</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>President decides</t>
+          <t>Till President desires</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Can appeal to remain</t>
+          <t>As long as he/she has majority support</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Disqualified immediately</t>
+          <t>As long as he/she has majority support</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>As per RPA 1951 and SC rulings, such a person loses membership and hence PMship.</t>
+          <t>There is no fixed term; it depends on majority in Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which PM was in power during Pokhran-II nuclear tests in 1998?</t>
+          <t>The resignation of the Prime Minister means the resignation of</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Only PM</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>PM and Vice President</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Entire Council of Ministers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Only Cabinet Ministers</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Entire Council of Ministers</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>He ordered the nuclear tests shortly after becoming PM.</t>
+          <t>Since the PM is head, his resignation dissolves the Council.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Who has the final authority to decide on the portfolios of Union Ministers?</t>
+          <t>The Prime Minister can be a member of which of the following?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Only Lok Sabha</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Only Rajya Sabha</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cabinet Secretary</t>
+          <t>Any House</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cabinet Committee</t>
+          <t>Only Legislative Assembly</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Any House</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>The PM allocates portfolios and can reshuffle them at will.</t>
+          <t>PM can be from Lok Sabha or Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>During whose Prime Ministership was the Emergency declared in 1975?</t>
+          <t>Which PM's government passed the 73rd and 74th Constitutional Amendments?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>She declared Emergency under Article 352.</t>
+          <t>These Acts gave constitutional status to Panchayati Raj and municipalities.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>When does the Prime Minister tender resignation?</t>
+          <t>What is the tenure of Prime Minister of India?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>After term completion</t>
+          <t>Fixed 5 years</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>After President’s directive</t>
+          <t>Fixed 6 years</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>After defeat in election</t>
+          <t>Depends on President</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>After losing Lok Sabha majority</t>
+          <t>No fixed tenure</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>After losing Lok Sabha majority</t>
+          <t>No fixed tenure</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>If PM loses support, he must resign.</t>
+          <t>PM holds office during the pleasure of the President, as long as majority is maintained.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>How many times has the office of Prime Minister been held by someone from Rajya Sabha?</t>
+          <t>Which constitutional article allows the PM to recommend President's Rule in a state?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Article 365</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Indira Gandhi, HD Deve Gowda, and Manmohan Singh have served while being Rajya Sabha members.</t>
+          <t>It allows the President to impose President’s Rule based on Governor’s or PM’s recommendation.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which Article establishes the Council of Ministers with the Prime Minister at the head?</t>
+          <t>Which Prime Minister nationalized 14 major banks in India?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>It provides for a Council of Ministers headed by the PM to aid and advise the President.</t>
+          <t>This was done in 1969 as part of socialist economic reforms.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which Prime Minister nationalized 14 major banks in India?</t>
+          <t>Which Article establishes the Council of Ministers with the Prime Minister at the head?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>This was done in 1969 as part of socialist economic reforms.</t>
+          <t>It provides for a Council of Ministers headed by the PM to aid and advise the President.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which constitutional article allows the PM to recommend President's Rule in a state?</t>
+          <t>How many times has the office of Prime Minister been held by someone from Rajya Sabha?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Article 365</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>It allows the President to impose President’s Rule based on Governor’s or PM’s recommendation.</t>
+          <t>Indira Gandhi, HD Deve Gowda, and Manmohan Singh have served while being Rajya Sabha members.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>What is the tenure of Prime Minister of India?</t>
+          <t>When does the Prime Minister tender resignation?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fixed 5 years</t>
+          <t>After term completion</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Fixed 6 years</t>
+          <t>After President’s directive</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Depends on President</t>
+          <t>After defeat in election</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>No fixed tenure</t>
+          <t>After losing Lok Sabha majority</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>No fixed tenure</t>
+          <t>After losing Lok Sabha majority</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>PM holds office during the pleasure of the President, as long as majority is maintained.</t>
+          <t>If PM loses support, he must resign.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which PM's government passed the 73rd and 74th Constitutional Amendments?</t>
+          <t>During whose Prime Ministership was the Emergency declared in 1975?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>These Acts gave constitutional status to Panchayati Raj and municipalities.</t>
+          <t>She declared Emergency under Article 352.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Prime Minister can be a member of which of the following?</t>
+          <t>Who has the final authority to decide on the portfolios of Union Ministers?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Only Lok Sabha</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Only Rajya Sabha</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Any House</t>
+          <t>Cabinet Secretary</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Only Legislative Assembly</t>
+          <t>Cabinet Committee</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Any House</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>PM can be from Lok Sabha or Rajya Sabha.</t>
+          <t>The PM allocates portfolios and can reshuffle them at will.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister to lose a confidence vote in Lok Sabha?</t>
+          <t>Which Prime Minister initiated the 'Look East Policy'?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>PV Narasimha Rao</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>Indira Gandhi</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>VP Singh</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>PV Narasimha Rao</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>He lost majority in 1979 and resigned before facing a vote.</t>
+          <t>He initiated the policy to strengthen relations with Southeast Asia.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Who was the first female Prime Minister of India?</t>
+          <t>Which Schedule of the Indian Constitution is indirectly related to the responsibilities of the Prime Minister?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sushma Swaraj</t>
+          <t>2nd Schedule</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>3rd Schedule</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Meira Kumar</t>
+          <t>7th Schedule</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>3rd Schedule</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>She became PM in 1966.</t>
+          <t>It contains the oath of office and secrecy taken by the PM and other ministers.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>If the Prime Minister dies suddenly, who becomes the Acting PM?</t>
+          <t>Which Prime Minister was in office during the Kargil War?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Senior-most Cabinet Minister</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Home Minister</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>No provision</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Senior-most Cabinet Minister</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Conventionally, the senior-most is asked to act until a new leader is chosen.</t>
+          <t>The Kargil conflict occurred in 1999 during his tenure.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which PM led the Janata Dal government formed after the Mandal Commission recommendations?</t>
+          <t>In which year was the post of Deputy Prime Minister first created in India?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>IK Gujral</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>He implemented the Mandal Commission recommendations in 1990.</t>
+          <t>Sardar Vallabhbhai Patel was the first Deputy PM in 1947.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which PM was referred to as the 'Chanakya of Indian Politics'?</t>
+          <t>What is the minimum educational qualification required to become Prime Minister in India?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Graduate</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>12th pass</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>No formal qualification</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Postgraduate</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>No formal qualification</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Known for his political strategies and handling of minority government.</t>
+          <t>The Constitution doesn’t prescribe any educational qualification.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What is the minimum educational qualification required to become Prime Minister in India?</t>
+          <t>Which PM was referred to as the 'Chanakya of Indian Politics'?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Graduate</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>12th pass</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>No formal qualification</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Postgraduate</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>No formal qualification</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>The Constitution doesn’t prescribe any educational qualification.</t>
+          <t>Known for his political strategies and handling of minority government.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>In which year was the post of Deputy Prime Minister first created in India?</t>
+          <t>Which PM led the Janata Dal government formed after the Mandal Commission recommendations?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>IK Gujral</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sardar Vallabhbhai Patel was the first Deputy PM in 1947.</t>
+          <t>He implemented the Mandal Commission recommendations in 1990.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which Prime Minister was in office during the Kargil War?</t>
+          <t>If the Prime Minister dies suddenly, who becomes the Acting PM?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Senior-most Cabinet Minister</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Home Minister</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>No provision</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Senior-most Cabinet Minister</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>The Kargil conflict occurred in 1999 during his tenure.</t>
+          <t>Conventionally, the senior-most is asked to act until a new leader is chosen.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which Schedule of the Indian Constitution is indirectly related to the responsibilities of the Prime Minister?</t>
+          <t>Who was the first female Prime Minister of India?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2nd Schedule</t>
+          <t>Sushma Swaraj</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3rd Schedule</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>7th Schedule</t>
+          <t>Meira Kumar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3rd Schedule</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>It contains the oath of office and secrecy taken by the PM and other ministers.</t>
+          <t>She became PM in 1966.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which Prime Minister initiated the 'Look East Policy'?</t>
+          <t>Who was the first Prime Minister to lose a confidence vote in Lok Sabha?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PV Narasimha Rao</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>Atal Bihari Vajpayee</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>VP Singh</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Atal Bihari Vajpayee</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Manmohan Singh</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>PV Narasimha Rao</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>He initiated the policy to strengthen relations with Southeast Asia.</t>
+          <t>He lost majority in 1979 and resigned before facing a vote.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>How long can a person remain Prime Minister without being a member of either House of Parliament?</t>
+          <t>The Prime Minister is the head of which body?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Indefinitely</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>He/she must become a member within 6 months.</t>
+          <t>The PM is the head of the Council of Ministers and leads the executive branch.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which PM was awarded the Bharat Ratna posthumously in 1991?</t>
+          <t>Which Prime Minister set up the Sarkaria Commission on Centre-State relations?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>Indira Gandhi</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>Rajiv Gandhi</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Indira Gandhi</t>
-        </is>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2530,352 +2530,352 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>He was assassinated in 1991 and awarded the Bharat Ratna posthumously.</t>
+          <t>The commission was set up in 1983 during his tenure.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which of the following committees is headed by the PM and deals with internal security?</t>
+          <t>Which of the following is a discretionary power of the President regarding the Prime Minister?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Political Affairs Committee</t>
+          <t>Dismissal</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Appointments Committee</t>
+          <t>Appointment when no party has majority</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Security Committee</t>
+          <t>Salary fixation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cabinet Committee on Security</t>
+          <t>Policy review</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cabinet Committee on Security</t>
+          <t>Appointment when no party has majority</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>This committee deals with defense and internal security issues.</t>
+          <t>In case of no clear majority, President has discretion in appointing the PM.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which Article empowers the President to act in accordance with the advice of the Council of Ministers headed by PM?</t>
+          <t>What is the significance of the expression "pleasure of the President" in context of PM's tenure?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Article 74(1)</t>
+          <t>Symbolic</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Article 75(3)</t>
+          <t>President can remove at will</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>PM can be dismissed anytime</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Article 78</t>
+          <t>Depends on Lok Sabha majority</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Article 74(1)</t>
+          <t>Depends on Lok Sabha majority</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>After the 42nd and 44th Amendments, the President is bound by the CoM's advice.</t>
+          <t>Though appointed by President, PM must enjoy majority support in Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The Prime Minister can be removed by</t>
+          <t>Under which constitutional amendment is the advice of the Council of Ministers to the President made binding?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>38th Amendment</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Impeachment</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lok Sabha via no-confidence motion</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lok Sabha via no-confidence motion</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>A successful no-confidence motion removes the PM.</t>
+          <t>The 42nd Amendment (1976) made Presidential advice binding.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Under which constitutional amendment is the advice of the Council of Ministers to the President made binding?</t>
+          <t>The Prime Minister can be removed by</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>38th Amendment</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Impeachment</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Lok Sabha via no-confidence motion</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Lok Sabha via no-confidence motion</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>The 42nd Amendment (1976) made Presidential advice binding.</t>
+          <t>A successful no-confidence motion removes the PM.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>What is the significance of the expression "pleasure of the President" in context of PM's tenure?</t>
+          <t>Which Article empowers the President to act in accordance with the advice of the Council of Ministers headed by PM?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Symbolic</t>
+          <t>Article 74(1)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>President can remove at will</t>
+          <t>Article 75(3)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PM can be dismissed anytime</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Depends on Lok Sabha majority</t>
+          <t>Article 78</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Depends on Lok Sabha majority</t>
+          <t>Article 74(1)</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Though appointed by President, PM must enjoy majority support in Lok Sabha.</t>
+          <t>After the 42nd and 44th Amendments, the President is bound by the CoM's advice.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which of the following is a discretionary power of the President regarding the Prime Minister?</t>
+          <t>Which of the following committees is headed by the PM and deals with internal security?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dismissal</t>
+          <t>Political Affairs Committee</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Appointment when no party has majority</t>
+          <t>Appointments Committee</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salary fixation</t>
+          <t>Security Committee</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Policy review</t>
+          <t>Cabinet Committee on Security</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Appointment when no party has majority</t>
+          <t>Cabinet Committee on Security</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>In case of no clear majority, President has discretion in appointing the PM.</t>
+          <t>This committee deals with defense and internal security issues.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which Prime Minister set up the Sarkaria Commission on Centre-State relations?</t>
+          <t>Which PM was awarded the Bharat Ratna posthumously in 1991?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>Rajiv Gandhi</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Lal Bahadur Shastri</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Jawaharlal Nehru</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
         <is>
           <t>Rajiv Gandhi</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Morarji Desai</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>P V Narasimha Rao</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Rajiv Gandhi</t>
-        </is>
-      </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>The commission was set up in 1983 during his tenure.</t>
+          <t>He was assassinated in 1991 and awarded the Bharat Ratna posthumously.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Prime Minister is the head of which body?</t>
+          <t>How long can a person remain Prime Minister without being a member of either House of Parliament?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Indefinitely</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>The PM is the head of the Council of Ministers and leads the executive branch.</t>
+          <t>He/she must become a member within 6 months.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which Prime Minister's term saw the introduction of MGNREGA?</t>
+          <t>Which Prime Minister implemented the Green Revolution policies?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2885,353 +2885,353 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>MGNREGA was launched in 2006 under his leadership.</t>
+          <t>Green Revolution was accelerated during her tenure.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>What is the position of the Prime Minister in the Union Cabinet?</t>
+          <t>The PM acts as a channel of communication between the President and</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Junior Minister</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Head of Cabinet</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nominal Head</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>Parliament</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Council of Ministers</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Head of Cabinet</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>The PM is the head and coordinates its functions.</t>
+          <t>PM is the link between President and CoM as per Article 78.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which Prime Minister’s government fell due to the withdrawal of support by AIADMK in 1999?</t>
+          <t>Which of the following events did **not** require the PM to face a no-confidence motion?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IK Gujral</t>
+          <t>Emergency of 1975</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Demolition of Babri Masjid</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Kargil War</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>Indira Gandhi’s election verdict</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Demolition of Babri Masjid</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>His government fell by one vote in 1999 after AIADMK withdrew support.</t>
+          <t>Though controversial, the PM wasn’t asked to prove majority immediately after it.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>In which landmark case did the Supreme Court observe that the Prime Minister is the "chief spokesman of the government"?</t>
+          <t>Which Prime Minister was a recipient of Bharat Ratna before becoming PM?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>S.P. Gupta case</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Keshavananda Bharati case</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Shamsher Singh case</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SR Bommai case</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Shamsher Singh case</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>This case clarified the role of PM in the cabinet system under parliamentary democracy.</t>
+          <t>He received Bharat Ratna in 1991, after retirement.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which of these Prime Ministers was never a Member of Lok Sabha?</t>
+          <t>The Prime Minister’s Office (PMO) is</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Statutory body</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Constitutional body</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Extra-constitutional body</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Judicial body</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Extra-constitutional body</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>He was a member of Rajya Sabha during his PM tenure.</t>
+          <t>The PMO is not mentioned in the Constitution but exists in practice.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Prime Minister’s Office (PMO) is</t>
+          <t>Which of these Prime Ministers was never a Member of Lok Sabha?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Statutory body</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Constitutional body</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Extra-constitutional body</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Judicial body</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Extra-constitutional body</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>The PMO is not mentioned in the Constitution but exists in practice.</t>
+          <t>He was a member of Rajya Sabha during his PM tenure.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which Prime Minister was a recipient of Bharat Ratna before becoming PM?</t>
+          <t>In which landmark case did the Supreme Court observe that the Prime Minister is the "chief spokesman of the government"?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>S.P. Gupta case</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Keshavananda Bharati case</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Shamsher Singh case</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>SR Bommai case</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Shamsher Singh case</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>He received Bharat Ratna in 1991, after retirement.</t>
+          <t>This case clarified the role of PM in the cabinet system under parliamentary democracy.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which of the following events did **not** require the PM to face a no-confidence motion?</t>
+          <t>Which Prime Minister’s government fell due to the withdrawal of support by AIADMK in 1999?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Emergency of 1975</t>
+          <t>IK Gujral</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Demolition of Babri Masjid</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kargil War</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Indira Gandhi’s election verdict</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Demolition of Babri Masjid</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Though controversial, the PM wasn’t asked to prove majority immediately after it.</t>
+          <t>His government fell by one vote in 1999 after AIADMK withdrew support.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The PM acts as a channel of communication between the President and</t>
+          <t>What is the position of the Prime Minister in the Union Cabinet?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Junior Minister</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Head of Cabinet</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Parliament</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Council of Ministers</t>
-        </is>
-      </c>
+          <t>Nominal Head</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Head of Cabinet</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>PM is the link between President and CoM as per Article 78.</t>
+          <t>The PM is the head and coordinates its functions.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which Prime Minister implemented the Green Revolution policies?</t>
+          <t>Which Prime Minister's term saw the introduction of MGNREGA?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3241,1212 +3241,1212 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Green Revolution was accelerated during her tenure.</t>
+          <t>MGNREGA was launched in 2006 under his leadership.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which PM is associated with the Golden Quadrilateral highway project?</t>
+          <t>Who acted as Prime Minister in between Jawaharlal Nehru's death and Lal Bahadur Shastri's appointment?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>K Kamaraj</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>The project was launched during his tenure as part of NHDP.</t>
+          <t>He served as interim PM after Nehru's death in 1964.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which Prime Minister had the shortest time between assuming office and facing a no-confidence motion?</t>
+          <t>The Prime Minister must be a member of which House?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee (1996)</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IK Gujral</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Only Lok Sabha</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee (1996)</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>He faced and lost a no-confidence vote within 13 days.</t>
+          <t>The PM can be a member of either Lok Sabha or Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Prime Minister is described as which of the following?</t>
+          <t>Which Article of the Constitution deals with the Prime Minister?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>First among equals</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Above all ministers</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Constitutional dictator</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Presiding officer</t>
+          <t>Article 78</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>First among equals</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>The PM is the keystone of the cabinet system and is the senior-most.</t>
+          <t>Article 75 provides for the appointment of the Prime Minister and other ministers.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>If the Prime Minister is a member of Rajya Sabha, which of the following is true?</t>
+          <t>Which Prime Minister of India was not a member of Parliament at the time of appointment?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cannot take part in debates</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cannot vote in Lok Sabha</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cannot be PM</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Must resign from Rajya Sabha</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cannot vote in Lok Sabha</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>A Rajya Sabha MP can participate but not vote in Lok Sabha.</t>
+          <t>He was appointed PM and later contested elections.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which Prime Minister signed the Simla Agreement in 1972?</t>
+          <t>Who advises the President on the appointment of other ministers?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Cabinet Secretary</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>It was signed with Pakistan after the 1971 war.</t>
+          <t>President appoints ministers on advice of the PM.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Who advises the President on the appointment of other ministers?</t>
+          <t>Which Prime Minister signed the Simla Agreement in 1972?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cabinet Secretary</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>President appoints ministers on advice of the PM.</t>
+          <t>It was signed with Pakistan after the 1971 war.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which Prime Minister of India was not a member of Parliament at the time of appointment?</t>
+          <t>If the Prime Minister is a member of Rajya Sabha, which of the following is true?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Cannot take part in debates</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Cannot vote in Lok Sabha</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Cannot be PM</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Must resign from Rajya Sabha</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Cannot vote in Lok Sabha</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>He was appointed PM and later contested elections.</t>
+          <t>A Rajya Sabha MP can participate but not vote in Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution deals with the Prime Minister?</t>
+          <t>The Prime Minister is described as which of the following?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>First among equals</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Above all ministers</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Constitutional dictator</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Article 78</t>
+          <t>Presiding officer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>First among equals</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Article 75 provides for the appointment of the Prime Minister and other ministers.</t>
+          <t>The PM is the keystone of the cabinet system and is the senior-most.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Prime Minister must be a member of which House?</t>
+          <t>Which Prime Minister had the shortest time between assuming office and facing a no-confidence motion?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Atal Bihari Vajpayee (1996)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>IK Gujral</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Only Lok Sabha</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Atal Bihari Vajpayee (1996)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>The PM can be a member of either Lok Sabha or Rajya Sabha.</t>
+          <t>He faced and lost a no-confidence vote within 13 days.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Who acted as Prime Minister in between Jawaharlal Nehru's death and Lal Bahadur Shastri's appointment?</t>
+          <t>Which PM is associated with the Golden Quadrilateral highway project?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>K Kamaraj</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>He served as interim PM after Nehru's death in 1964.</t>
+          <t>The project was launched during his tenure as part of NHDP.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Who administers the oath of office to the Prime Minister?</t>
+          <t>The Prime Minister is responsible to which body?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>Rajya Sabha</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Lok Sabha</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Vice President</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Speaker of Lok Sabha</t>
-        </is>
-      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>The President administers the oath of office and secrecy to the PM.</t>
+          <t>The PM is collectively responsible to the Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Under which circumstances can the Prime Minister recommend dissolution of Lok Sabha to the President?</t>
+          <t>Which Prime Minister had the longest uninterrupted tenure?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Only after a confidence vote</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Only with Cabinet approval</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Only after consulting Speaker</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>The PM can advise dissolution anytime, subject to constitutional propriety.</t>
+          <t>He served continuously for 17 years from 1947 to 1964.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which Prime Minister was also a Reserve Bank Governor?</t>
+          <t>Which Prime Minister was in office when the Anti-Defection Law was passed?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>He served as RBI Governor from 1982–1985.</t>
+          <t>The 52nd Amendment Act, 1985 was passed during Rajiv Gandhi's tenure.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The Prime Minister is the leader of which house by convention?</t>
+          <t>The Prime Minister communicates to the President all decisions of the Council of Ministers under which Article?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Article 78</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Council of States</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Upper House</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Article 78</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Although not mandatory, the PM usually leads the Lok Sabha.</t>
+          <t>It is the duty of the PM to inform the President of all cabinet decisions.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Can a person from outside Parliament be appointed as PM?</t>
+          <t>The Prime Minister is not mentioned by name in which part of the Constitution?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Part V</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Yes, for 3 months</t>
+          <t>Part VI</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Yes, for 6 months</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Only if nominated</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Yes, for 6 months</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>He/she must get elected to Parliament within 6 months.</t>
+          <t>Fundamental Rights make no mention of the PM; it is dealt with in Part V (Union).</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The Prime Minister is not mentioned by name in which part of the Constitution?</t>
+          <t>Can a person from outside Parliament be appointed as PM?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Part V</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Part VI</t>
+          <t>Yes, for 3 months</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>Yes, for 6 months</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Only if nominated</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>Yes, for 6 months</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Fundamental Rights make no mention of the PM; it is dealt with in Part V (Union).</t>
+          <t>He/she must get elected to Parliament within 6 months.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The Prime Minister communicates to the President all decisions of the Council of Ministers under which Article?</t>
+          <t>The Prime Minister is the leader of which house by convention?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Article 78</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Council of States</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>Upper House</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Article 78</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>It is the duty of the PM to inform the President of all cabinet decisions.</t>
+          <t>Although not mandatory, the PM usually leads the Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which Prime Minister was in office when the Anti-Defection Law was passed?</t>
+          <t>Which Prime Minister was also a Reserve Bank Governor?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t>Morarji Desai</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>VP Singh</t>
-        </is>
-      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>The 52nd Amendment Act, 1985 was passed during Rajiv Gandhi's tenure.</t>
+          <t>He served as RBI Governor from 1982–1985.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which Prime Minister had the longest uninterrupted tenure?</t>
+          <t>Under which circumstances can the Prime Minister recommend dissolution of Lok Sabha to the President?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Any time</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Only after a confidence vote</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Only with Cabinet approval</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Only after consulting Speaker</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Any time</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>He served continuously for 17 years from 1947 to 1964.</t>
+          <t>The PM can advise dissolution anytime, subject to constitutional propriety.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The Prime Minister is responsible to which body?</t>
+          <t>Who administers the oath of office to the Prime Minister?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
+          <t>Speaker of Lok Sabha</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Lok Sabha</t>
-        </is>
-      </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>The PM is collectively responsible to the Lok Sabha.</t>
+          <t>The President administers the oath of office and secrecy to the PM.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which of the following Prime Ministers never faced Parliament during their tenure?</t>
+          <t>Who was India’s first non-Congress Prime Minister?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
+          <t>VP Singh</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
           <t>Morarji Desai</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Gulzarilal Nanda</t>
-        </is>
-      </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>He was caretaker PM twice, without facing Parliament.</t>
+          <t>He became PM in 1977 from the Janata Party.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which committee is headed by the Prime Minister?</t>
+          <t>Which of the following Prime Ministers served two non-consecutive terms?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Estimates Committee</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Planning Commission</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>PM is the ex-officio Chairperson of NITI Aayog.</t>
+          <t>He served briefly in 1996 and then from 1998 to 2004.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which Prime Minister abolished the Privy Purses of former princely rulers?</t>
+          <t>Which of the following is **not** a Cabinet Committee chaired by the Prime Minister?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Appointments Committee</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Political Affairs Committee</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Economic Affairs Committee</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Parliamentary Standing Committee</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Parliamentary Standing Committee</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>The move was made via a Constitutional Amendment in 1971.</t>
+          <t>These are headed by MPs or Speaker, not PM.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which PM was heading a coalition but completed a full 5-year term for the first time?</t>
+          <t>Which Prime Minister initiated the policy of Economic Liberalization in India?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>IK Gujral</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>He led the NDA government from 1999–2004 successfully.</t>
+          <t>His government started reforms in 1991 with Manmohan Singh as Finance Minister.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>The Prime Minister acts as a link between</t>
+          <t>Who is known as the 'Father of Indian Economic Reforms'?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>President and Parliament</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cabinet and Judiciary</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Parliament and States</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>President and Cabinet</t>
+          <t>PV Narasimha Rao</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>President and Cabinet</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>PM communicates Cabinet decisions to the President.</t>
+          <t>As Finance Minister in 1991, he launched liberalization reforms.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Who is known as the 'Father of Indian Economic Reforms'?</t>
+          <t>The Prime Minister acts as a link between</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>President and Parliament</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Cabinet and Judiciary</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Parliament and States</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>PV Narasimha Rao</t>
+          <t>President and Cabinet</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>President and Cabinet</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>As Finance Minister in 1991, he launched liberalization reforms.</t>
+          <t>PM communicates Cabinet decisions to the President.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which Prime Minister initiated the policy of Economic Liberalization in India?</t>
+          <t>Which PM was heading a coalition but completed a full 5-year term for the first time?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t>IK Gujral</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>Manmohan Singh</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>P V Narasimha Rao</t>
-        </is>
-      </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>His government started reforms in 1991 with Manmohan Singh as Finance Minister.</t>
+          <t>He led the NDA government from 1999–2004 successfully.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which of the following is **not** a Cabinet Committee chaired by the Prime Minister?</t>
+          <t>Which Prime Minister abolished the Privy Purses of former princely rulers?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Appointments Committee</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Political Affairs Committee</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Economic Affairs Committee</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Parliamentary Standing Committee</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Parliamentary Standing Committee</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>These are headed by MPs or Speaker, not PM.</t>
+          <t>The move was made via a Constitutional Amendment in 1971.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which of the following Prime Ministers served two non-consecutive terms?</t>
+          <t>Which committee is headed by the Prime Minister?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Estimates Committee</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Planning Commission</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>He served briefly in 1996 and then from 1998 to 2004.</t>
+          <t>PM is the ex-officio Chairperson of NITI Aayog.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Who was India’s first non-Congress Prime Minister?</t>
+          <t>Which of the following Prime Ministers never faced Parliament during their tenure?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
+          <t>Gulzarilal Nanda</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Lal Bahadur Shastri</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>Morarji Desai</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Charan Singh</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>VP Singh</t>
-        </is>
-      </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>He became PM in 1977 from the Janata Party.</t>
+          <t>He was caretaker PM twice, without facing Parliament.</t>
         </is>
       </c>
     </row>

--- a/Data/IPPrimeminister.xlsx
+++ b/Data/IPPrimeminister.xlsx
@@ -472,251 +472,247 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which Article indirectly recognizes the existence of the Prime Minister without naming the post?</t>
+          <t>What is the position of the Prime Minister in the Union Cabinet?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Junior Minister</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Head of Cabinet</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Article 53</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Article 50</t>
-        </is>
-      </c>
+          <t>Nominal Head</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Head of Cabinet</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>It mentions a Council of Ministers headed by the PM.</t>
+          <t>The PM is the head and coordinates its functions.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Who was the youngest Prime Minister of India?</t>
+          <t>Can a person from outside Parliament be appointed as PM?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Yes, for 3 months</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Yes, for 6 months</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Only if nominated</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Yes, for 6 months</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>He became PM at the age of 40.</t>
+          <t>He/she must get elected to Parliament within 6 months.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which Prime Minister gave the slogan 'Garibi Hatao'?</t>
+          <t>Who appoints the Prime Minister of India?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>She gave this slogan during the 1971 election campaign.</t>
+          <t>The President formally appoints the PM, usually the leader of the majority in Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Who appoints the Prime Minister of India?</t>
+          <t>Which of these Prime Ministers was never a Member of Lok Sabha?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>The President formally appoints the PM, usually the leader of the majority in Lok Sabha.</t>
+          <t>He was a member of Rajya Sabha during his PM tenure.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which PM passed away while in office outside India?</t>
+          <t>Who presides over the meetings of the Union Council of Ministers?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>He died in Tashkent (USSR) after signing the Tashkent Agreement in 1966.</t>
+          <t>The PM is the head of the Council and chairs its meetings.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Who presides over the meetings of the Union Council of Ministers?</t>
+          <t>Which Prime Minister nationalized 14 major banks in India?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>The PM is the head of the Council and chairs its meetings.</t>
+          <t>This was done in 1969 as part of socialist economic reforms.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which Prime Minister launched the 20-Point Programme in 1975?</t>
+          <t>Which Prime Minister introduced the slogan 'Minimum Government, Maximum Governance'?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -726,134 +722,134 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Manmohan Singh</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Narendra Modi</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Indira Gandhi</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VP Singh</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>It was a socio-economic initiative launched during the Emergency.</t>
+          <t>It was part of his 2014 election campaign vision.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>In the case of death or resignation of Prime Minister, who appoints the new PM?</t>
+          <t>Which PM was referred to as the 'Chanakya of Indian Politics'?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>The President appoints the new Prime Minister based on majority support.</t>
+          <t>Known for his political strategies and handling of minority government.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which Prime Minister faced the most number of no-confidence motions?</t>
+          <t>Which of the following events did **not** require the PM to face a no-confidence motion?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Emergency of 1975</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Demolition of Babri Masjid</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Kargil War</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Indira Gandhi’s election verdict</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Demolition of Babri Masjid</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>She faced the most no-confidence motions during her tenure.</t>
+          <t>Though controversial, the PM wasn’t asked to prove majority immediately after it.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which Prime Minister introduced the slogan 'Minimum Government, Maximum Governance'?</t>
+          <t>Which PM's government passed the 73rd and 74th Constitutional Amendments?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>P V Narasimha Rao</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>Rajiv Gandhi</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Manmohan Singh</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Narendra Modi</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Atal Bihari Vajpayee</t>
@@ -861,134 +857,142 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>It was part of his 2014 election campaign vision.</t>
+          <t>These Acts gave constitutional status to Panchayati Raj and municipalities.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which PM’s tenure saw the passage of the RTI Act?</t>
+          <t>Under Article 75(3), the Council of Ministers is collectively responsible to which House?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Both Houses</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Right to Information Act was passed in 2005.</t>
+          <t>This ensures accountability of executive to the lower house.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Who among the following served as both Prime Minister and President of India?</t>
+          <t>The Prime Minister is the ex-officio Chairman of which of the following?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>V V Giri</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>Planning Board</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>National Integration Council</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>National Integration Council</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>No one has held both posts; they are distinct positions.</t>
+          <t>PM chairs this council promoting national unity.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which of the following statements is true about PM’s resignation?</t>
+          <t>Which Prime Minister launched the 20-Point Programme in 1975?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>It must be accepted by President</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>It is effective immediately</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>It must be in writing</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>It is reviewed by Supreme Court</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>It must be accepted by President</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Resignation becomes effective once accepted by the President.</t>
+          <t>It was a socio-economic initiative launched during the Emergency.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Who succeeded Lal Bahadur Shastri as Prime Minister?</t>
+          <t>Which Prime Minister was arrested during the British Quit India Movement?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -998,269 +1002,277 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>She took over as PM in 1966 after Shastri’s death.</t>
+          <t>He was imprisoned multiple times during the freedom movement.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Who can ask the Prime Minister to prove majority in Lok Sabha?</t>
+          <t>The Prime Minister acts as a link between</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>President and Parliament</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Cabinet and Judiciary</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Parliament and States</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>President and Cabinet</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>President and Cabinet</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>If doubt arises, President can ask PM to prove majority.</t>
+          <t>PM communicates Cabinet decisions to the President.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which one of the following is not a function of the Prime Minister?</t>
+          <t>In which landmark case did the Supreme Court observe that the Prime Minister is the "chief spokesman of the government"?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Allocating portfolios</t>
+          <t>S.P. Gupta case</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Presiding over cabinet meetings</t>
+          <t>Keshavananda Bharati case</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dismissing ministers</t>
+          <t>Shamsher Singh case</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Advising President</t>
+          <t>SR Bommai case</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dismissing ministers</t>
+          <t>Shamsher Singh case</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Only the President can formally dismiss ministers on PM’s advice.</t>
+          <t>This case clarified the role of PM in the cabinet system under parliamentary democracy.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Who served as PM after the assassination of Indira Gandhi?</t>
+          <t>Who was the youngest Prime Minister of India?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>Rajiv Gandhi</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Narendra Modi</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Morarji Desai</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Rajiv Gandhi</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Gulzarilal Nanda</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Rajiv Gandhi</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>He was immediately sworn in after her assassination in 1984.</t>
+          <t>He became PM at the age of 40.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which Prime Minister lost a motion of confidence but refused to resign, leading to a constitutional crisis?</t>
+          <t>Which Article empowers the President to act in accordance with the advice of the Council of Ministers headed by PM?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Article 74(1)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Article 75(3)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+          <t>Article 76</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Article 78</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Article 74(1)</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>All PMs respected the no-confidence result and resigned accordingly.</t>
+          <t>After the 42nd and 44th Amendments, the President is bound by the CoM's advice.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Prime Minister is the ex-officio Chairman of which of the following?</t>
+          <t>The term of office of the Prime Minister is</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Planning Board</t>
+          <t>Till President desires</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>National Integration Council</t>
+          <t>As long as he/she has majority support</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>National Integration Council</t>
+          <t>As long as he/she has majority support</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>PM chairs this council promoting national unity.</t>
+          <t>There is no fixed term; it depends on majority in Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>What happens if the Prime Minister loses majority support in Lok Sabha?</t>
+          <t>Who served as PM after the assassination of Indira Gandhi?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dismissed by President</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Resigns</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Continues till term ends</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Impeached</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Resigns</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Losing majority means the PM must resign.</t>
+          <t>He was immediately sworn in after her assassination in 1984.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which PM was in power during Pokhran-II nuclear tests in 1998?</t>
+          <t>Which Prime Minister was also a Reserve Bank Governor?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1270,179 +1282,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>He ordered the nuclear tests shortly after becoming PM.</t>
+          <t>He served as RBI Governor from 1982–1985.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>If a Prime Minister is convicted in a criminal case and sentenced for more than 2 years, what happens?</t>
+          <t>Which Prime Minister of India was not a member of Parliament at the time of appointment?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Can continue</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Disqualified immediately</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>President decides</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Can appeal to remain</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Disqualified immediately</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>As per RPA 1951 and SC rulings, such a person loses membership and hence PMship.</t>
+          <t>He was appointed PM and later contested elections.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Under Article 75(3), the Council of Ministers is collectively responsible to which House?</t>
+          <t>Who was the first female Prime Minister of India?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Sushma Swaraj</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Both Houses</t>
+          <t>Meira Kumar</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>This ensures accountability of executive to the lower house.</t>
+          <t>She became PM in 1966.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which Prime Minister was arrested during the British Quit India Movement?</t>
+          <t>Which of the following is **not** a Cabinet Committee chaired by the Prime Minister?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Appointments Committee</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Political Affairs Committee</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Economic Affairs Committee</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Parliamentary Standing Committee</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Parliamentary Standing Committee</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>He was imprisoned multiple times during the freedom movement.</t>
+          <t>These are headed by MPs or Speaker, not PM.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which PM faced criticism for Operation Blue Star?</t>
+          <t>Which Prime Minister signed the Simla Agreement in 1972?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Atal Bihari Vajpayee</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Lal Bahadur Shastri</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>Rajiv Gandhi</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Manmohan Singh</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Morarji Desai</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>Indira Gandhi</t>
@@ -1450,2513 +1462,2509 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>She ordered the military operation at the Golden Temple in 1984.</t>
+          <t>It was signed with Pakistan after the 1971 war.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which Prime Minister had the shortest tenure?</t>
+          <t>The Prime Minister is the head of which body?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee (1996)</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee (1996)</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>He served for just 13 days before resigning.</t>
+          <t>The PM is the head of the Council of Ministers and leads the executive branch.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Prime Minister’s advisory role to the President is</t>
+          <t>Which Prime Minister was in office during the Kargil War?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Discretionary</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ceremonial</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Under Article 74(1), advice of CoM led by PM is binding.</t>
+          <t>The Kargil conflict occurred in 1999 during his tenure.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What is the difference between Cabinet and Council of Ministers in context of PM’s role?</t>
+          <t>Which PM passed away while in office outside India?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No difference</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cabinet is a part of CoM</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PM heads Cabinet only</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Only Cabinet advises President</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cabinet is a part of CoM</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>PM leads both, but Cabinet is an inner core of senior ministers.</t>
+          <t>He died in Tashkent (USSR) after signing the Tashkent Agreement in 1966.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The term of office of the Prime Minister is</t>
+          <t>Which Prime Minister had the shortest time between assuming office and facing a no-confidence motion?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Atal Bihari Vajpayee (1996)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Till President desires</t>
+          <t>IK Gujral</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>As long as he/she has majority support</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>As long as he/she has majority support</t>
+          <t>Atal Bihari Vajpayee (1996)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>There is no fixed term; it depends on majority in Lok Sabha.</t>
+          <t>He faced and lost a no-confidence vote within 13 days.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The resignation of the Prime Minister means the resignation of</t>
+          <t>Which Prime Minister lost a motion of confidence but refused to resign, leading to a constitutional crisis?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Only PM</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PM and Vice President</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Entire Council of Ministers</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Only Cabinet Ministers</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Entire Council of Ministers</t>
-        </is>
-      </c>
+          <t>Indira Gandhi</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Since the PM is head, his resignation dissolves the Council.</t>
+          <t>All PMs respected the no-confidence result and resigned accordingly.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Prime Minister can be a member of which of the following?</t>
+          <t>Which PM faced criticism for Operation Blue Star?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Only Lok Sabha</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Only Rajya Sabha</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Any House</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Only Legislative Assembly</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Any House</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>PM can be from Lok Sabha or Rajya Sabha.</t>
+          <t>She ordered the military operation at the Golden Temple in 1984.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which PM's government passed the 73rd and 74th Constitutional Amendments?</t>
+          <t>Which PM led the Janata Dal government formed after the Mandal Commission recommendations?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>IK Gujral</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>These Acts gave constitutional status to Panchayati Raj and municipalities.</t>
+          <t>He implemented the Mandal Commission recommendations in 1990.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What is the tenure of Prime Minister of India?</t>
+          <t>Which Schedule of the Indian Constitution is indirectly related to the responsibilities of the Prime Minister?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fixed 5 years</t>
+          <t>2nd Schedule</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fixed 6 years</t>
+          <t>3rd Schedule</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Depends on President</t>
+          <t>7th Schedule</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>No fixed tenure</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>No fixed tenure</t>
+          <t>3rd Schedule</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>PM holds office during the pleasure of the President, as long as majority is maintained.</t>
+          <t>It contains the oath of office and secrecy taken by the PM and other ministers.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which constitutional article allows the PM to recommend President's Rule in a state?</t>
+          <t>Which of the following Prime Ministers never faced Parliament during their tenure?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Article 365</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>It allows the President to impose President’s Rule based on Governor’s or PM’s recommendation.</t>
+          <t>He was caretaker PM twice, without facing Parliament.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which Prime Minister nationalized 14 major banks in India?</t>
+          <t>Which PM is associated with the Golden Quadrilateral highway project?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>This was done in 1969 as part of socialist economic reforms.</t>
+          <t>The project was launched during his tenure as part of NHDP.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which Article establishes the Council of Ministers with the Prime Minister at the head?</t>
+          <t>In the case of death or resignation of Prime Minister, who appoints the new PM?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>It provides for a Council of Ministers headed by the PM to aid and advise the President.</t>
+          <t>The President appoints the new Prime Minister based on majority support.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>How many times has the office of Prime Minister been held by someone from Rajya Sabha?</t>
+          <t>Which PM’s tenure saw the passage of the RTI Act?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Indira Gandhi, HD Deve Gowda, and Manmohan Singh have served while being Rajya Sabha members.</t>
+          <t>Right to Information Act was passed in 2005.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>When does the Prime Minister tender resignation?</t>
+          <t>The Prime Minister can be removed by</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>After term completion</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>After President’s directive</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>After defeat in election</t>
+          <t>Impeachment</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>After losing Lok Sabha majority</t>
+          <t>Lok Sabha via no-confidence motion</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>After losing Lok Sabha majority</t>
+          <t>Lok Sabha via no-confidence motion</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>If PM loses support, he must resign.</t>
+          <t>A successful no-confidence motion removes the PM.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>During whose Prime Ministership was the Emergency declared in 1975?</t>
+          <t>Which Article establishes the Council of Ministers with the Prime Minister at the head?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>She declared Emergency under Article 352.</t>
+          <t>It provides for a Council of Ministers headed by the PM to aid and advise the President.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Who has the final authority to decide on the portfolios of Union Ministers?</t>
+          <t>Which Prime Minister implemented the Green Revolution policies?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cabinet Secretary</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cabinet Committee</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>The PM allocates portfolios and can reshuffle them at will.</t>
+          <t>Green Revolution was accelerated during her tenure.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which Prime Minister initiated the 'Look East Policy'?</t>
+          <t>What is the minimum educational qualification required to become Prime Minister in India?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PV Narasimha Rao</t>
+          <t>Graduate</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>12th pass</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>No formal qualification</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Postgraduate</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PV Narasimha Rao</t>
+          <t>No formal qualification</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>He initiated the policy to strengthen relations with Southeast Asia.</t>
+          <t>The Constitution doesn’t prescribe any educational qualification.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which Schedule of the Indian Constitution is indirectly related to the responsibilities of the Prime Minister?</t>
+          <t>Which Prime Minister initiated the 'Look East Policy'?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2nd Schedule</t>
+          <t>PV Narasimha Rao</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3rd Schedule</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>7th Schedule</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3rd Schedule</t>
+          <t>PV Narasimha Rao</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>It contains the oath of office and secrecy taken by the PM and other ministers.</t>
+          <t>He initiated the policy to strengthen relations with Southeast Asia.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which Prime Minister was in office during the Kargil War?</t>
+          <t>Which Prime Minister's term saw the introduction of MGNREGA?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>Atal Bihari Vajpayee</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Manmohan Singh</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Narendra Modi</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>Rajiv Gandhi</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Atal Bihari Vajpayee</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>P V Narasimha Rao</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Manmohan Singh</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Atal Bihari Vajpayee</t>
-        </is>
-      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>The Kargil conflict occurred in 1999 during his tenure.</t>
+          <t>MGNREGA was launched in 2006 under his leadership.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>In which year was the post of Deputy Prime Minister first created in India?</t>
+          <t>Which of the following is a discretionary power of the President regarding the Prime Minister?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Dismissal</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Appointment when no party has majority</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>Salary fixation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>Policy review</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Appointment when no party has majority</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sardar Vallabhbhai Patel was the first Deputy PM in 1947.</t>
+          <t>In case of no clear majority, President has discretion in appointing the PM.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>What is the minimum educational qualification required to become Prime Minister in India?</t>
+          <t>The Prime Minister’s advisory role to the President is</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Graduate</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>12th pass</t>
+          <t>Discretionary</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>No formal qualification</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Postgraduate</t>
+          <t>Ceremonial</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>No formal qualification</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>The Constitution doesn’t prescribe any educational qualification.</t>
+          <t>Under Article 74(1), advice of CoM led by PM is binding.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which PM was referred to as the 'Chanakya of Indian Politics'?</t>
+          <t>Which of the following statements is true about PM’s resignation?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>It must be accepted by President</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>It is effective immediately</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>It must be in writing</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>It is reviewed by Supreme Court</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>It must be accepted by President</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Known for his political strategies and handling of minority government.</t>
+          <t>Resignation becomes effective once accepted by the President.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which PM led the Janata Dal government formed after the Mandal Commission recommendations?</t>
+          <t>Who administers the oath of office to the Prime Minister?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>IK Gujral</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>He implemented the Mandal Commission recommendations in 1990.</t>
+          <t>The President administers the oath of office and secrecy to the PM.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>If the Prime Minister dies suddenly, who becomes the Acting PM?</t>
+          <t>Which one of the following is not a function of the Prime Minister?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Allocating portfolios</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Senior-most Cabinet Minister</t>
+          <t>Presiding over cabinet meetings</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Home Minister</t>
+          <t>Dismissing ministers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>No provision</t>
+          <t>Advising President</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Senior-most Cabinet Minister</t>
+          <t>Dismissing ministers</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Conventionally, the senior-most is asked to act until a new leader is chosen.</t>
+          <t>Only the President can formally dismiss ministers on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who was the first female Prime Minister of India?</t>
+          <t>Which PM was in power during Pokhran-II nuclear tests in 1998?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sushma Swaraj</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Meira Kumar</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>She became PM in 1966.</t>
+          <t>He ordered the nuclear tests shortly after becoming PM.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister to lose a confidence vote in Lok Sabha?</t>
+          <t>What happens if the Prime Minister loses majority support in Lok Sabha?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Dismissed by President</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Resigns</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Continues till term ends</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Impeached</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Resigns</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>He lost majority in 1979 and resigned before facing a vote.</t>
+          <t>Losing majority means the PM must resign.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Prime Minister is the head of which body?</t>
+          <t>Which Article indirectly recognizes the existence of the Prime Minister without naming the post?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>The PM is the head of the Council of Ministers and leads the executive branch.</t>
+          <t>It mentions a Council of Ministers headed by the PM.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which Prime Minister set up the Sarkaria Commission on Centre-State relations?</t>
+          <t>Which Prime Minister abolished the Privy Purses of former princely rulers?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>Lal Bahadur Shastri</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Jawaharlal Nehru</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Rajiv Gandhi</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Morarji Desai</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>P V Narasimha Rao</t>
-        </is>
-      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>The commission was set up in 1983 during his tenure.</t>
+          <t>The move was made via a Constitutional Amendment in 1971.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which of the following is a discretionary power of the President regarding the Prime Minister?</t>
+          <t>Who has the final authority to decide on the portfolios of Union Ministers?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dismissal</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Appointment when no party has majority</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Salary fixation</t>
+          <t>Cabinet Secretary</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Policy review</t>
+          <t>Cabinet Committee</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Appointment when no party has majority</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>In case of no clear majority, President has discretion in appointing the PM.</t>
+          <t>The PM allocates portfolios and can reshuffle them at will.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>What is the significance of the expression "pleasure of the President" in context of PM's tenure?</t>
+          <t>Which Prime Minister had the longest uninterrupted tenure?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Symbolic</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>President can remove at will</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PM can be dismissed anytime</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Depends on Lok Sabha majority</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Depends on Lok Sabha majority</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Though appointed by President, PM must enjoy majority support in Lok Sabha.</t>
+          <t>He served continuously for 17 years from 1947 to 1964.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Under which constitutional amendment is the advice of the Council of Ministers to the President made binding?</t>
+          <t>Who succeeded Lal Bahadur Shastri as Prime Minister?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>38th Amendment</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>The 42nd Amendment (1976) made Presidential advice binding.</t>
+          <t>She took over as PM in 1966 after Shastri’s death.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Prime Minister can be removed by</t>
+          <t>The Prime Minister is the leader of which house by convention?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Impeachment</t>
+          <t>Council of States</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lok Sabha via no-confidence motion</t>
+          <t>Upper House</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lok Sabha via no-confidence motion</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>A successful no-confidence motion removes the PM.</t>
+          <t>Although not mandatory, the PM usually leads the Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which Article empowers the President to act in accordance with the advice of the Council of Ministers headed by PM?</t>
+          <t>How many times has the office of Prime Minister been held by someone from Rajya Sabha?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Article 74(1)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Article 75(3)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Article 78</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Article 74(1)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>After the 42nd and 44th Amendments, the President is bound by the CoM's advice.</t>
+          <t>Indira Gandhi, HD Deve Gowda, and Manmohan Singh have served while being Rajya Sabha members.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which of the following committees is headed by the PM and deals with internal security?</t>
+          <t>Who was the first Prime Minister to lose a confidence vote in Lok Sabha?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Political Affairs Committee</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Appointments Committee</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Security Committee</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cabinet Committee on Security</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cabinet Committee on Security</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>This committee deals with defense and internal security issues.</t>
+          <t>He lost majority in 1979 and resigned before facing a vote.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which PM was awarded the Bharat Ratna posthumously in 1991?</t>
+          <t>Which Prime Minister faced the most number of no-confidence motions?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>Indira Gandhi</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Jawaharlal Nehru</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>Rajiv Gandhi</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Atal Bihari Vajpayee</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
         <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Lal Bahadur Shastri</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Jawaharlal Nehru</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Rajiv Gandhi</t>
-        </is>
-      </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>He was assassinated in 1991 and awarded the Bharat Ratna posthumously.</t>
+          <t>She faced the most no-confidence motions during her tenure.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>How long can a person remain Prime Minister without being a member of either House of Parliament?</t>
+          <t>Which of the following Prime Ministers served two non-consecutive terms?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Indefinitely</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>He/she must become a member within 6 months.</t>
+          <t>He served briefly in 1996 and then from 1998 to 2004.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which Prime Minister implemented the Green Revolution policies?</t>
+          <t>Which PM was awarded the Bharat Ratna posthumously in 1991?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>Rajiv Gandhi</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Indira Gandhi</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Lal Bahadur Shastri</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>Jawaharlal Nehru</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Lal Bahadur Shastri</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Indira Gandhi</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Rajiv Gandhi</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Indira Gandhi</t>
-        </is>
-      </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Green Revolution was accelerated during her tenure.</t>
+          <t>He was assassinated in 1991 and awarded the Bharat Ratna posthumously.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The PM acts as a channel of communication between the President and</t>
+          <t>The Prime Minister must be a member of which House?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Only Lok Sabha</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>PM is the link between President and CoM as per Article 78.</t>
+          <t>The PM can be a member of either Lok Sabha or Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which of the following events did **not** require the PM to face a no-confidence motion?</t>
+          <t>Under which constitutional amendment is the advice of the Council of Ministers to the President made binding?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Emergency of 1975</t>
+          <t>38th Amendment</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Demolition of Babri Masjid</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kargil War</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Indira Gandhi’s election verdict</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Demolition of Babri Masjid</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Though controversial, the PM wasn’t asked to prove majority immediately after it.</t>
+          <t>The 42nd Amendment (1976) made Presidential advice binding.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which Prime Minister was a recipient of Bharat Ratna before becoming PM?</t>
+          <t>In which year was the post of Deputy Prime Minister first created in India?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>He received Bharat Ratna in 1991, after retirement.</t>
+          <t>Sardar Vallabhbhai Patel was the first Deputy PM in 1947.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Prime Minister’s Office (PMO) is</t>
+          <t>Which Prime Minister was a recipient of Bharat Ratna before becoming PM?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Statutory body</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Constitutional body</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Extra-constitutional body</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Judicial body</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Extra-constitutional body</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>The PMO is not mentioned in the Constitution but exists in practice.</t>
+          <t>He received Bharat Ratna in 1991, after retirement.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which of these Prime Ministers was never a Member of Lok Sabha?</t>
+          <t>The Prime Minister can be a member of which of the following?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Only Lok Sabha</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Only Rajya Sabha</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Any House</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Only Legislative Assembly</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Any House</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>He was a member of Rajya Sabha during his PM tenure.</t>
+          <t>PM can be from Lok Sabha or Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>In which landmark case did the Supreme Court observe that the Prime Minister is the "chief spokesman of the government"?</t>
+          <t>What is the significance of the expression "pleasure of the President" in context of PM's tenure?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>S.P. Gupta case</t>
+          <t>Symbolic</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Keshavananda Bharati case</t>
+          <t>President can remove at will</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Shamsher Singh case</t>
+          <t>PM can be dismissed anytime</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SR Bommai case</t>
+          <t>Depends on Lok Sabha majority</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Shamsher Singh case</t>
+          <t>Depends on Lok Sabha majority</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>This case clarified the role of PM in the cabinet system under parliamentary democracy.</t>
+          <t>Though appointed by President, PM must enjoy majority support in Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which Prime Minister’s government fell due to the withdrawal of support by AIADMK in 1999?</t>
+          <t>Who acted as Prime Minister in between Jawaharlal Nehru's death and Lal Bahadur Shastri's appointment?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IK Gujral</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>K Kamaraj</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>His government fell by one vote in 1999 after AIADMK withdrew support.</t>
+          <t>He served as interim PM after Nehru's death in 1964.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>What is the position of the Prime Minister in the Union Cabinet?</t>
+          <t>The Prime Minister is described as which of the following?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Junior Minister</t>
+          <t>First among equals</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Head of Cabinet</t>
+          <t>Above all ministers</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nominal Head</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
+          <t>Constitutional dictator</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Presiding officer</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Head of Cabinet</t>
+          <t>First among equals</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>The PM is the head and coordinates its functions.</t>
+          <t>The PM is the keystone of the cabinet system and is the senior-most.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which Prime Minister's term saw the introduction of MGNREGA?</t>
+          <t>When does the Prime Minister tender resignation?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>After term completion</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>After President’s directive</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>After defeat in election</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>After losing Lok Sabha majority</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>After losing Lok Sabha majority</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>MGNREGA was launched in 2006 under his leadership.</t>
+          <t>If PM loses support, he must resign.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Who acted as Prime Minister in between Jawaharlal Nehru's death and Lal Bahadur Shastri's appointment?</t>
+          <t>If a Prime Minister is convicted in a criminal case and sentenced for more than 2 years, what happens?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Can continue</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Disqualified immediately</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>President decides</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>K Kamaraj</t>
+          <t>Can appeal to remain</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Disqualified immediately</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>He served as interim PM after Nehru's death in 1964.</t>
+          <t>As per RPA 1951 and SC rulings, such a person loses membership and hence PMship.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Prime Minister must be a member of which House?</t>
+          <t>Who can ask the Prime Minister to prove majority in Lok Sabha?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Only Lok Sabha</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>The PM can be a member of either Lok Sabha or Rajya Sabha.</t>
+          <t>If doubt arises, President can ask PM to prove majority.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution deals with the Prime Minister?</t>
+          <t>Which Prime Minister was in office when the Anti-Defection Law was passed?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Article 78</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Article 75 provides for the appointment of the Prime Minister and other ministers.</t>
+          <t>The 52nd Amendment Act, 1985 was passed during Rajiv Gandhi's tenure.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which Prime Minister of India was not a member of Parliament at the time of appointment?</t>
+          <t>If the Prime Minister is a member of Rajya Sabha, which of the following is true?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Cannot take part in debates</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Cannot vote in Lok Sabha</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Cannot be PM</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Must resign from Rajya Sabha</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Cannot vote in Lok Sabha</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>He was appointed PM and later contested elections.</t>
+          <t>A Rajya Sabha MP can participate but not vote in Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Who advises the President on the appointment of other ministers?</t>
+          <t>Which Prime Minister set up the Sarkaria Commission on Centre-State relations?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cabinet Secretary</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>President appoints ministers on advice of the PM.</t>
+          <t>The commission was set up in 1983 during his tenure.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which Prime Minister signed the Simla Agreement in 1972?</t>
+          <t>Who was India’s first non-Congress Prime Minister?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>It was signed with Pakistan after the 1971 war.</t>
+          <t>He became PM in 1977 from the Janata Party.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>If the Prime Minister is a member of Rajya Sabha, which of the following is true?</t>
+          <t>The Prime Minister’s Office (PMO) is</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cannot take part in debates</t>
+          <t>Statutory body</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cannot vote in Lok Sabha</t>
+          <t>Constitutional body</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cannot be PM</t>
+          <t>Extra-constitutional body</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Must resign from Rajya Sabha</t>
+          <t>Judicial body</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cannot vote in Lok Sabha</t>
+          <t>Extra-constitutional body</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>A Rajya Sabha MP can participate but not vote in Lok Sabha.</t>
+          <t>The PMO is not mentioned in the Constitution but exists in practice.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Prime Minister is described as which of the following?</t>
+          <t>The Prime Minister is not mentioned by name in which part of the Constitution?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>First among equals</t>
+          <t>Part V</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Above all ministers</t>
+          <t>Part VI</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Constitutional dictator</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Presiding officer</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>First among equals</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>The PM is the keystone of the cabinet system and is the senior-most.</t>
+          <t>Fundamental Rights make no mention of the PM; it is dealt with in Part V (Union).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which Prime Minister had the shortest time between assuming office and facing a no-confidence motion?</t>
+          <t>Which Prime Minister initiated the policy of Economic Liberalization in India?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee (1996)</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>IK Gujral</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee (1996)</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>He faced and lost a no-confidence vote within 13 days.</t>
+          <t>His government started reforms in 1991 with Manmohan Singh as Finance Minister.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which PM is associated with the Golden Quadrilateral highway project?</t>
+          <t>The PM acts as a channel of communication between the President and</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>The project was launched during his tenure as part of NHDP.</t>
+          <t>PM is the link between President and CoM as per Article 78.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The Prime Minister is responsible to which body?</t>
+          <t>Which PM was heading a coalition but completed a full 5-year term for the first time?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>IK Gujral</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>The PM is collectively responsible to the Lok Sabha.</t>
+          <t>He led the NDA government from 1999–2004 successfully.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which Prime Minister had the longest uninterrupted tenure?</t>
+          <t>Who advises the President on the appointment of other ministers?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Cabinet Secretary</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>He served continuously for 17 years from 1947 to 1964.</t>
+          <t>President appoints ministers on advice of the PM.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which Prime Minister was in office when the Anti-Defection Law was passed?</t>
+          <t>The Prime Minister is responsible to which body?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>The 52nd Amendment Act, 1985 was passed during Rajiv Gandhi's tenure.</t>
+          <t>The PM is collectively responsible to the Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The Prime Minister communicates to the President all decisions of the Council of Ministers under which Article?</t>
+          <t>Which Article of the Constitution deals with the Prime Minister?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>Article 74</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
           <t>Article 75</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Article 76</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Article 78</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Article 80</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Article 85</t>
-        </is>
-      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Article 78</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>It is the duty of the PM to inform the President of all cabinet decisions.</t>
+          <t>Article 75 provides for the appointment of the Prime Minister and other ministers.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The Prime Minister is not mentioned by name in which part of the Constitution?</t>
+          <t>Under which circumstances can the Prime Minister recommend dissolution of Lok Sabha to the President?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Part V</t>
+          <t>Any time</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Part VI</t>
+          <t>Only after a confidence vote</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>Only with Cabinet approval</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Only after consulting Speaker</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>Any time</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Fundamental Rights make no mention of the PM; it is dealt with in Part V (Union).</t>
+          <t>The PM can advise dissolution anytime, subject to constitutional propriety.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Can a person from outside Parliament be appointed as PM?</t>
+          <t>During whose Prime Ministership was the Emergency declared in 1975?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Yes, for 3 months</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Yes, for 6 months</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Only if nominated</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Yes, for 6 months</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>He/she must get elected to Parliament within 6 months.</t>
+          <t>She declared Emergency under Article 352.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The Prime Minister is the leader of which house by convention?</t>
+          <t>Which Prime Minister had the shortest tenure?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Council of States</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Upper House</t>
+          <t>Atal Bihari Vajpayee (1996)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Atal Bihari Vajpayee (1996)</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Although not mandatory, the PM usually leads the Lok Sabha.</t>
+          <t>He served for just 13 days before resigning.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which Prime Minister was also a Reserve Bank Governor?</t>
+          <t>Who is known as the 'Father of Indian Economic Reforms'?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>Atal Bihari Vajpayee</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Indira Gandhi</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>Manmohan Singh</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Morarji Desai</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Indira Gandhi</t>
-        </is>
-      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>PV Narasimha Rao</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3966,487 +3974,479 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>He served as RBI Governor from 1982–1985.</t>
+          <t>As Finance Minister in 1991, he launched liberalization reforms.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Under which circumstances can the Prime Minister recommend dissolution of Lok Sabha to the President?</t>
+          <t>How long can a person remain Prime Minister without being a member of either House of Parliament?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Only after a confidence vote</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Only with Cabinet approval</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Only after consulting Speaker</t>
+          <t>Indefinitely</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>The PM can advise dissolution anytime, subject to constitutional propriety.</t>
+          <t>He/she must become a member within 6 months.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Who administers the oath of office to the Prime Minister?</t>
+          <t>The resignation of the Prime Minister means the resignation of</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Only PM</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>PM and Vice President</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Entire Council of Ministers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Only Cabinet Ministers</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Entire Council of Ministers</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>The President administers the oath of office and secrecy to the PM.</t>
+          <t>Since the PM is head, his resignation dissolves the Council.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Who was India’s first non-Congress Prime Minister?</t>
+          <t>Which constitutional article allows the PM to recommend President's Rule in a state?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Article 365</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>He became PM in 1977 from the Janata Party.</t>
+          <t>It allows the President to impose President’s Rule based on Governor’s or PM’s recommendation.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which of the following Prime Ministers served two non-consecutive terms?</t>
+          <t>What is the tenure of Prime Minister of India?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Fixed 5 years</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Fixed 6 years</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Depends on President</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>No fixed tenure</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>No fixed tenure</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>He served briefly in 1996 and then from 1998 to 2004.</t>
+          <t>PM holds office during the pleasure of the President, as long as majority is maintained.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which of the following is **not** a Cabinet Committee chaired by the Prime Minister?</t>
+          <t>Which of the following committees is headed by the PM and deals with internal security?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
+          <t>Political Affairs Committee</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
           <t>Appointments Committee</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Political Affairs Committee</t>
-        </is>
-      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Economic Affairs Committee</t>
+          <t>Security Committee</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Parliamentary Standing Committee</t>
+          <t>Cabinet Committee on Security</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Parliamentary Standing Committee</t>
+          <t>Cabinet Committee on Security</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>These are headed by MPs or Speaker, not PM.</t>
+          <t>This committee deals with defense and internal security issues.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which Prime Minister initiated the policy of Economic Liberalization in India?</t>
+          <t>Who among the following served as both Prime Minister and President of India?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>P V Narasimha Rao</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>P V Narasimha Rao</t>
-        </is>
-      </c>
+          <t>V V Giri</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>His government started reforms in 1991 with Manmohan Singh as Finance Minister.</t>
+          <t>No one has held both posts; they are distinct positions.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Who is known as the 'Father of Indian Economic Reforms'?</t>
+          <t>If the Prime Minister dies suddenly, who becomes the Acting PM?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Senior-most Cabinet Minister</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Home Minister</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PV Narasimha Rao</t>
+          <t>No provision</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Senior-most Cabinet Minister</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>As Finance Minister in 1991, he launched liberalization reforms.</t>
+          <t>Conventionally, the senior-most is asked to act until a new leader is chosen.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The Prime Minister acts as a link between</t>
+          <t>Which Prime Minister’s government fell due to the withdrawal of support by AIADMK in 1999?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>President and Parliament</t>
+          <t>IK Gujral</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Cabinet and Judiciary</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Parliament and States</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>President and Cabinet</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>President and Cabinet</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>PM communicates Cabinet decisions to the President.</t>
+          <t>His government fell by one vote in 1999 after AIADMK withdrew support.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which PM was heading a coalition but completed a full 5-year term for the first time?</t>
+          <t>What is the difference between Cabinet and Council of Ministers in context of PM’s role?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>No difference</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>IK Gujral</t>
+          <t>Cabinet is a part of CoM</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>PM heads Cabinet only</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Only Cabinet advises President</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Cabinet is a part of CoM</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>He led the NDA government from 1999–2004 successfully.</t>
+          <t>PM leads both, but Cabinet is an inner core of senior ministers.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which Prime Minister abolished the Privy Purses of former princely rulers?</t>
+          <t>Which Prime Minister gave the slogan 'Garibi Hatao'?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
+          <t>Rajiv Gandhi</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
           <t>Lal Bahadur Shastri</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Indira Gandhi</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>Jawaharlal Nehru</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Rajiv Gandhi</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Indira Gandhi</t>
-        </is>
-      </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>The move was made via a Constitutional Amendment in 1971.</t>
+          <t>She gave this slogan during the 1971 election campaign.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which committee is headed by the Prime Minister?</t>
+          <t>The Prime Minister communicates to the President all decisions of the Council of Ministers under which Article?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Estimates Committee</t>
+          <t>Article 78</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Planning Commission</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>Article 78</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>PM is the ex-officio Chairperson of NITI Aayog.</t>
+          <t>It is the duty of the PM to inform the President of all cabinet decisions.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which of the following Prime Ministers never faced Parliament during their tenure?</t>
+          <t>Which committee is headed by the Prime Minister?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Estimates Committee</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Planning Commission</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>He was caretaker PM twice, without facing Parliament.</t>
+          <t>PM is the ex-officio Chairperson of NITI Aayog.</t>
         </is>
       </c>
     </row>

--- a/Data/IPPrimeminister.xlsx
+++ b/Data/IPPrimeminister.xlsx
@@ -472,127 +472,131 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What is the position of the Prime Minister in the Union Cabinet?</t>
+          <t>Which Article empowers the President to act in accordance with the advice of the Council of Ministers headed by PM?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Junior Minister</t>
+          <t>Article 74(1)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Head of Cabinet</t>
+          <t>Article 75(3)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nominal Head</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>Article 76</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Article 78</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Head of Cabinet</t>
+          <t>Article 74(1)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The PM is the head and coordinates its functions.</t>
+          <t>After the 42nd and 44th Amendments, the President is bound by the CoM's advice.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Can a person from outside Parliament be appointed as PM?</t>
+          <t>The Prime Minister is the ex-officio Chairman of which of the following?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Yes, for 3 months</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yes, for 6 months</t>
+          <t>Planning Board</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Only if nominated</t>
+          <t>National Integration Council</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes, for 6 months</t>
+          <t>National Integration Council</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>He/she must get elected to Parliament within 6 months.</t>
+          <t>PM chairs this council promoting national unity.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Who appoints the Prime Minister of India?</t>
+          <t>Can a person from outside Parliament be appointed as PM?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Yes, for 3 months</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Yes, for 6 months</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Only if nominated</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Yes, for 6 months</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>The President formally appoints the PM, usually the leader of the majority in Lok Sabha.</t>
+          <t>He/she must get elected to Parliament within 6 months.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which of these Prime Ministers was never a Member of Lok Sabha?</t>
+          <t>Who was India’s first non-Congress Prime Minister?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -602,37 +606,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>VP Singh</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>Morarji Desai</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Manmohan Singh</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>He was a member of Rajya Sabha during his PM tenure.</t>
+          <t>He became PM in 1977 from the Janata Party.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Who presides over the meetings of the Union Council of Ministers?</t>
+          <t>Who appoints the Prime Minister of India?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -642,77 +646,77 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>The PM is the head of the Council and chairs its meetings.</t>
+          <t>The President formally appoints the PM, usually the leader of the majority in Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which Prime Minister nationalized 14 major banks in India?</t>
+          <t>The Prime Minister can be a member of which of the following?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Only Lok Sabha</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Only Rajya Sabha</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Any House</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Only Legislative Assembly</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Any House</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>This was done in 1969 as part of socialist economic reforms.</t>
+          <t>PM can be from Lok Sabha or Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which Prime Minister introduced the slogan 'Minimum Government, Maximum Governance'?</t>
+          <t>Which Prime Minister was in office when the Anti-Defection Law was passed?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -722,67 +726,67 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>It was part of his 2014 election campaign vision.</t>
+          <t>The 52nd Amendment Act, 1985 was passed during Rajiv Gandhi's tenure.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which PM was referred to as the 'Chanakya of Indian Politics'?</t>
+          <t>What is the difference between Cabinet and Council of Ministers in context of PM’s role?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>No difference</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Cabinet is a part of CoM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>PM heads Cabinet only</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Only Cabinet advises President</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Cabinet is a part of CoM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Known for his political strategies and handling of minority government.</t>
+          <t>PM leads both, but Cabinet is an inner core of senior ministers.</t>
         </is>
       </c>
     </row>
@@ -828,1505 +832,1505 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which PM's government passed the 73rd and 74th Constitutional Amendments?</t>
+          <t>The Prime Minister acts as a link between</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>President and Parliament</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Cabinet and Judiciary</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Parliament and States</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>President and Cabinet</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>President and Cabinet</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>These Acts gave constitutional status to Panchayati Raj and municipalities.</t>
+          <t>PM communicates Cabinet decisions to the President.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Under Article 75(3), the Council of Ministers is collectively responsible to which House?</t>
+          <t>Which PM was in power during Pokhran-II nuclear tests in 1998?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Both Houses</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>This ensures accountability of executive to the lower house.</t>
+          <t>He ordered the nuclear tests shortly after becoming PM.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Prime Minister is the ex-officio Chairman of which of the following?</t>
+          <t>The resignation of the Prime Minister means the resignation of</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Only PM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>PM and Vice President</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Planning Board</t>
+          <t>Entire Council of Ministers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>National Integration Council</t>
+          <t>Only Cabinet Ministers</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>National Integration Council</t>
+          <t>Entire Council of Ministers</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PM chairs this council promoting national unity.</t>
+          <t>Since the PM is head, his resignation dissolves the Council.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which Prime Minister launched the 20-Point Programme in 1975?</t>
+          <t>If the Prime Minister dies suddenly, who becomes the Acting PM?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Senior-most Cabinet Minister</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Home Minister</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>No provision</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Senior-most Cabinet Minister</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>It was a socio-economic initiative launched during the Emergency.</t>
+          <t>Conventionally, the senior-most is asked to act until a new leader is chosen.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which Prime Minister was arrested during the British Quit India Movement?</t>
+          <t>Which of the following Prime Ministers never faced Parliament during their tenure?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Gulzarilal Nanda</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Jawaharlal Nehru</t>
-        </is>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>He was imprisoned multiple times during the freedom movement.</t>
+          <t>He was caretaker PM twice, without facing Parliament.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Prime Minister acts as a link between</t>
+          <t>Who is known as the 'Father of Indian Economic Reforms'?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>President and Parliament</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cabinet and Judiciary</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Parliament and States</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>President and Cabinet</t>
+          <t>PV Narasimha Rao</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>President and Cabinet</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>PM communicates Cabinet decisions to the President.</t>
+          <t>As Finance Minister in 1991, he launched liberalization reforms.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>In which landmark case did the Supreme Court observe that the Prime Minister is the "chief spokesman of the government"?</t>
+          <t>What is the minimum educational qualification required to become Prime Minister in India?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>S.P. Gupta case</t>
+          <t>Graduate</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Keshavananda Bharati case</t>
+          <t>12th pass</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shamsher Singh case</t>
+          <t>No formal qualification</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SR Bommai case</t>
+          <t>Postgraduate</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Shamsher Singh case</t>
+          <t>No formal qualification</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>This case clarified the role of PM in the cabinet system under parliamentary democracy.</t>
+          <t>The Constitution doesn’t prescribe any educational qualification.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Who was the youngest Prime Minister of India?</t>
+          <t>The Prime Minister must be a member of which House?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Only Lok Sabha</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>He became PM at the age of 40.</t>
+          <t>The PM can be a member of either Lok Sabha or Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which Article empowers the President to act in accordance with the advice of the Council of Ministers headed by PM?</t>
+          <t>The term of office of the Prime Minister is</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Article 74(1)</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Article 75(3)</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Till President desires</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Article 78</t>
+          <t>As long as he/she has majority support</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Article 74(1)</t>
+          <t>As long as he/she has majority support</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>After the 42nd and 44th Amendments, the President is bound by the CoM's advice.</t>
+          <t>There is no fixed term; it depends on majority in Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The term of office of the Prime Minister is</t>
+          <t>Which Article of the Constitution deals with the Prime Minister?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Till President desires</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>As long as he/she has majority support</t>
+          <t>Article 78</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>As long as he/she has majority support</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>There is no fixed term; it depends on majority in Lok Sabha.</t>
+          <t>Article 75 provides for the appointment of the Prime Minister and other ministers.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Who served as PM after the assassination of Indira Gandhi?</t>
+          <t>Which of the following is **not** a Cabinet Committee chaired by the Prime Minister?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Appointments Committee</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Political Affairs Committee</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Economic Affairs Committee</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Parliamentary Standing Committee</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Parliamentary Standing Committee</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>He was immediately sworn in after her assassination in 1984.</t>
+          <t>These are headed by MPs or Speaker, not PM.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which Prime Minister was also a Reserve Bank Governor?</t>
+          <t>How long can a person remain Prime Minister without being a member of either House of Parliament?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Indefinitely</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>He served as RBI Governor from 1982–1985.</t>
+          <t>He/she must become a member within 6 months.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which Prime Minister of India was not a member of Parliament at the time of appointment?</t>
+          <t>Which Prime Minister was arrested during the British Quit India Movement?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>He was appointed PM and later contested elections.</t>
+          <t>He was imprisoned multiple times during the freedom movement.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Who was the first female Prime Minister of India?</t>
+          <t>The Prime Minister is not mentioned by name in which part of the Constitution?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sushma Swaraj</t>
+          <t>Part V</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Part VI</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Meira Kumar</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Part IV</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Part III</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>She became PM in 1966.</t>
+          <t>Fundamental Rights make no mention of the PM; it is dealt with in Part V (Union).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which of the following is **not** a Cabinet Committee chaired by the Prime Minister?</t>
+          <t>Who was the first Prime Minister to lose a confidence vote in Lok Sabha?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Appointments Committee</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Political Affairs Committee</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Economic Affairs Committee</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Parliamentary Standing Committee</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parliamentary Standing Committee</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>These are headed by MPs or Speaker, not PM.</t>
+          <t>He lost majority in 1979 and resigned before facing a vote.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which Prime Minister signed the Simla Agreement in 1972?</t>
+          <t>In which landmark case did the Supreme Court observe that the Prime Minister is the "chief spokesman of the government"?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>S.P. Gupta case</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Keshavananda Bharati case</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Shamsher Singh case</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>SR Bommai case</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Shamsher Singh case</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>It was signed with Pakistan after the 1971 war.</t>
+          <t>This case clarified the role of PM in the cabinet system under parliamentary democracy.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Prime Minister is the head of which body?</t>
+          <t>Which Prime Minister lost a motion of confidence but refused to resign, leading to a constitutional crisis?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Executive</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Election Commission</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Executive</t>
-        </is>
-      </c>
+          <t>Indira Gandhi</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>The PM is the head of the Council of Ministers and leads the executive branch.</t>
+          <t>All PMs respected the no-confidence result and resigned accordingly.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which Prime Minister was in office during the Kargil War?</t>
+          <t>Who presides over the meetings of the Union Council of Ministers?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>The Kargil conflict occurred in 1999 during his tenure.</t>
+          <t>The PM is the head of the Council and chairs its meetings.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which PM passed away while in office outside India?</t>
+          <t>Who acted as Prime Minister in between Jawaharlal Nehru's death and Lal Bahadur Shastri's appointment?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>K Kamaraj</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>He died in Tashkent (USSR) after signing the Tashkent Agreement in 1966.</t>
+          <t>He served as interim PM after Nehru's death in 1964.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which Prime Minister had the shortest time between assuming office and facing a no-confidence motion?</t>
+          <t>The Prime Minister can be removed by</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee (1996)</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IK Gujral</t>
+          <t>Impeachment</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Lok Sabha via no-confidence motion</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee (1996)</t>
+          <t>Lok Sabha via no-confidence motion</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>He faced and lost a no-confidence vote within 13 days.</t>
+          <t>A successful no-confidence motion removes the PM.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which Prime Minister lost a motion of confidence but refused to resign, leading to a constitutional crisis?</t>
+          <t>Which PM's government passed the 73rd and 74th Constitutional Amendments?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+          <t>Manmohan Singh</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Atal Bihari Vajpayee</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>P V Narasimha Rao</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>All PMs respected the no-confidence result and resigned accordingly.</t>
+          <t>These Acts gave constitutional status to Panchayati Raj and municipalities.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which PM faced criticism for Operation Blue Star?</t>
+          <t>Who succeeded Lal Bahadur Shastri as Prime Minister?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>Morarji Desai</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Gulzarilal Nanda</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Charan Singh</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Manmohan Singh</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Morarji Desai</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Indira Gandhi</t>
-        </is>
-      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>She ordered the military operation at the Golden Temple in 1984.</t>
+          <t>She took over as PM in 1966 after Shastri’s death.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which PM led the Janata Dal government formed after the Mandal Commission recommendations?</t>
+          <t>Which PM was referred to as the 'Chanakya of Indian Politics'?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>Atal Bihari Vajpayee</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>P V Narasimha Rao</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Manmohan Singh</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>Charan Singh</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>HD Deve Gowda</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>VP Singh</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>IK Gujral</t>
-        </is>
-      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>He implemented the Mandal Commission recommendations in 1990.</t>
+          <t>Known for his political strategies and handling of minority government.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which Schedule of the Indian Constitution is indirectly related to the responsibilities of the Prime Minister?</t>
+          <t>Which Prime Minister of India was not a member of Parliament at the time of appointment?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2nd Schedule</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3rd Schedule</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>7th Schedule</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>10th Schedule</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3rd Schedule</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>It contains the oath of office and secrecy taken by the PM and other ministers.</t>
+          <t>He was appointed PM and later contested elections.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which of the following Prime Ministers never faced Parliament during their tenure?</t>
+          <t>Under Article 75(3), the Council of Ministers is collectively responsible to which House?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Both Houses</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>He was caretaker PM twice, without facing Parliament.</t>
+          <t>This ensures accountability of executive to the lower house.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which PM is associated with the Golden Quadrilateral highway project?</t>
+          <t>The Prime Minister is described as which of the following?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>First among equals</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Above all ministers</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Constitutional dictator</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Presiding officer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>First among equals</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>The project was launched during his tenure as part of NHDP.</t>
+          <t>The PM is the keystone of the cabinet system and is the senior-most.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>In the case of death or resignation of Prime Minister, who appoints the new PM?</t>
+          <t>Which PM’s tenure saw the passage of the RTI Act?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>The President appoints the new Prime Minister based on majority support.</t>
+          <t>Right to Information Act was passed in 2005.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which PM’s tenure saw the passage of the RTI Act?</t>
+          <t>Who advises the President on the appointment of other ministers?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Cabinet Secretary</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Right to Information Act was passed in 2005.</t>
+          <t>President appoints ministers on advice of the PM.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Prime Minister can be removed by</t>
+          <t>During whose Prime Ministership was the Emergency declared in 1975?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Impeachment</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lok Sabha via no-confidence motion</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lok Sabha via no-confidence motion</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>A successful no-confidence motion removes the PM.</t>
+          <t>She declared Emergency under Article 352.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which Article establishes the Council of Ministers with the Prime Minister at the head?</t>
+          <t>Which Prime Minister nationalized 14 major banks in India?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>It provides for a Council of Ministers headed by the PM to aid and advise the President.</t>
+          <t>This was done in 1969 as part of socialist economic reforms.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which Prime Minister implemented the Green Revolution policies?</t>
+          <t>Which of the following Prime Ministers served two non-consecutive terms?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Green Revolution was accelerated during her tenure.</t>
+          <t>He served briefly in 1996 and then from 1998 to 2004.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What is the minimum educational qualification required to become Prime Minister in India?</t>
+          <t>Which constitutional article allows the PM to recommend President's Rule in a state?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Graduate</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>12th pass</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>No formal qualification</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Postgraduate</t>
+          <t>Article 365</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>No formal qualification</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>The Constitution doesn’t prescribe any educational qualification.</t>
+          <t>It allows the President to impose President’s Rule based on Governor’s or PM’s recommendation.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which Prime Minister initiated the 'Look East Policy'?</t>
+          <t>Which Prime Minister was also a Reserve Bank Governor?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PV Narasimha Rao</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>Morarji Desai</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Atal Bihari Vajpayee</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>Lal Bahadur Shastri</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>Manmohan Singh</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>PV Narasimha Rao</t>
-        </is>
-      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>He initiated the policy to strengthen relations with Southeast Asia.</t>
+          <t>He served as RBI Governor from 1982–1985.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which Prime Minister's term saw the introduction of MGNREGA?</t>
+          <t>Which PM faced criticism for Operation Blue Star?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>Indira Gandhi</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>Manmohan Singh</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Narendra Modi</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>MGNREGA was launched in 2006 under his leadership.</t>
+          <t>She ordered the military operation at the Golden Temple in 1984.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which of the following is a discretionary power of the President regarding the Prime Minister?</t>
+          <t>Which of these Prime Ministers was never a Member of Lok Sabha?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dismissal</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Appointment when no party has majority</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Salary fixation</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Policy review</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Appointment when no party has majority</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>In case of no clear majority, President has discretion in appointing the PM.</t>
+          <t>He was a member of Rajya Sabha during his PM tenure.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Prime Minister’s advisory role to the President is</t>
+          <t>Which PM passed away while in office outside India?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Discretionary</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ceremonial</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Under Article 74(1), advice of CoM led by PM is binding.</t>
+          <t>He died in Tashkent (USSR) after signing the Tashkent Agreement in 1966.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which of the following statements is true about PM’s resignation?</t>
+          <t>What is the significance of the expression "pleasure of the President" in context of PM's tenure?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>It must be accepted by President</t>
+          <t>Symbolic</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>It is effective immediately</t>
+          <t>President can remove at will</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>It must be in writing</t>
+          <t>PM can be dismissed anytime</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>It is reviewed by Supreme Court</t>
+          <t>Depends on Lok Sabha majority</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>It must be accepted by President</t>
+          <t>Depends on Lok Sabha majority</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Resignation becomes effective once accepted by the President.</t>
+          <t>Though appointed by President, PM must enjoy majority support in Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Who administers the oath of office to the Prime Minister?</t>
+          <t>In the case of death or resignation of Prime Minister, who appoints the new PM?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>Lok Sabha</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Vice President</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Speaker of Lok Sabha</t>
-        </is>
-      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>President</t>
@@ -2334,457 +2338,457 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>The President administers the oath of office and secrecy to the PM.</t>
+          <t>The President appoints the new Prime Minister based on majority support.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which one of the following is not a function of the Prime Minister?</t>
+          <t>Which Prime Minister abolished the Privy Purses of former princely rulers?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Allocating portfolios</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Presiding over cabinet meetings</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dismissing ministers</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Advising President</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dismissing ministers</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Only the President can formally dismiss ministers on PM’s advice.</t>
+          <t>The move was made via a Constitutional Amendment in 1971.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which PM was in power during Pokhran-II nuclear tests in 1998?</t>
+          <t>If the Prime Minister is a member of Rajya Sabha, which of the following is true?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Cannot take part in debates</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Cannot vote in Lok Sabha</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Cannot be PM</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Must resign from Rajya Sabha</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Cannot vote in Lok Sabha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>He ordered the nuclear tests shortly after becoming PM.</t>
+          <t>A Rajya Sabha MP can participate but not vote in Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What happens if the Prime Minister loses majority support in Lok Sabha?</t>
+          <t>Which of the following is a discretionary power of the President regarding the Prime Minister?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dismissed by President</t>
+          <t>Dismissal</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Resigns</t>
+          <t>Appointment when no party has majority</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Continues till term ends</t>
+          <t>Salary fixation</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Impeached</t>
+          <t>Policy review</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Resigns</t>
+          <t>Appointment when no party has majority</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Losing majority means the PM must resign.</t>
+          <t>In case of no clear majority, President has discretion in appointing the PM.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which Article indirectly recognizes the existence of the Prime Minister without naming the post?</t>
+          <t>Which Prime Minister was in office during the Kargil War?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>It mentions a Council of Ministers headed by the PM.</t>
+          <t>The Kargil conflict occurred in 1999 during his tenure.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which Prime Minister abolished the Privy Purses of former princely rulers?</t>
+          <t>Which Prime Minister introduced the slogan 'Minimum Government, Maximum Governance'?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>The move was made via a Constitutional Amendment in 1971.</t>
+          <t>It was part of his 2014 election campaign vision.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Who has the final authority to decide on the portfolios of Union Ministers?</t>
+          <t>The Prime Minister’s Office (PMO) is</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Statutory body</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Constitutional body</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cabinet Secretary</t>
+          <t>Extra-constitutional body</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cabinet Committee</t>
+          <t>Judicial body</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Extra-constitutional body</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>The PM allocates portfolios and can reshuffle them at will.</t>
+          <t>The PMO is not mentioned in the Constitution but exists in practice.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which Prime Minister had the longest uninterrupted tenure?</t>
+          <t>When does the Prime Minister tender resignation?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>After term completion</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>After President’s directive</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>After defeat in election</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>After losing Lok Sabha majority</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>After losing Lok Sabha majority</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>He served continuously for 17 years from 1947 to 1964.</t>
+          <t>If PM loses support, he must resign.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Who succeeded Lal Bahadur Shastri as Prime Minister?</t>
+          <t>Which of the following statements is true about PM’s resignation?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>It must be accepted by President</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>It is effective immediately</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>It must be in writing</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>It is reviewed by Supreme Court</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>It must be accepted by President</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>She took over as PM in 1966 after Shastri’s death.</t>
+          <t>Resignation becomes effective once accepted by the President.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Prime Minister is the leader of which house by convention?</t>
+          <t>The Prime Minister communicates to the President all decisions of the Council of Ministers under which Article?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Article 78</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Council of States</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Upper House</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Article 78</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Although not mandatory, the PM usually leads the Lok Sabha.</t>
+          <t>It is the duty of the PM to inform the President of all cabinet decisions.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>How many times has the office of Prime Minister been held by someone from Rajya Sabha?</t>
+          <t>Which Prime Minister had the shortest tenure?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Atal Bihari Vajpayee (1996)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Atal Bihari Vajpayee (1996)</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Indira Gandhi, HD Deve Gowda, and Manmohan Singh have served while being Rajya Sabha members.</t>
+          <t>He served for just 13 days before resigning.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Who was the first Prime Minister to lose a confidence vote in Lok Sabha?</t>
+          <t>Which Schedule of the Indian Constitution is indirectly related to the responsibilities of the Prime Minister?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>2nd Schedule</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>3rd Schedule</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>7th Schedule</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>10th Schedule</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>3rd Schedule</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>He lost majority in 1979 and resigned before facing a vote.</t>
+          <t>It contains the oath of office and secrecy taken by the PM and other ministers.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which Prime Minister faced the most number of no-confidence motions?</t>
+          <t>Which Prime Minister initiated the policy of Economic Liberalization in India?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2794,1659 +2798,1655 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>She faced the most no-confidence motions during her tenure.</t>
+          <t>His government started reforms in 1991 with Manmohan Singh as Finance Minister.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which of the following Prime Ministers served two non-consecutive terms?</t>
+          <t>Which Article indirectly recognizes the existence of the Prime Minister without naming the post?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Narendra Modi</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>He served briefly in 1996 and then from 1998 to 2004.</t>
+          <t>It mentions a Council of Ministers headed by the PM.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which PM was awarded the Bharat Ratna posthumously in 1991?</t>
+          <t>Who has the final authority to decide on the portfolios of Union Ministers?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Cabinet Secretary</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Cabinet Committee</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>He was assassinated in 1991 and awarded the Bharat Ratna posthumously.</t>
+          <t>The PM allocates portfolios and can reshuffle them at will.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Prime Minister must be a member of which House?</t>
+          <t>Which Article establishes the Council of Ministers with the Prime Minister at the head?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Only Lok Sabha</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>The PM can be a member of either Lok Sabha or Rajya Sabha.</t>
+          <t>It provides for a Council of Ministers headed by the PM to aid and advise the President.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Under which constitutional amendment is the advice of the Council of Ministers to the President made binding?</t>
+          <t>What is the tenure of Prime Minister of India?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>38th Amendment</t>
+          <t>Fixed 5 years</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Fixed 6 years</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Depends on President</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>No fixed tenure</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>No fixed tenure</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>The 42nd Amendment (1976) made Presidential advice binding.</t>
+          <t>PM holds office during the pleasure of the President, as long as majority is maintained.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>In which year was the post of Deputy Prime Minister first created in India?</t>
+          <t>The Prime Minister is responsible to which body?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sardar Vallabhbhai Patel was the first Deputy PM in 1947.</t>
+          <t>The PM is collectively responsible to the Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which Prime Minister was a recipient of Bharat Ratna before becoming PM?</t>
+          <t>Which Prime Minister had the shortest time between assuming office and facing a no-confidence motion?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Atal Bihari Vajpayee (1996)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>IK Gujral</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Atal Bihari Vajpayee (1996)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>He received Bharat Ratna in 1991, after retirement.</t>
+          <t>He faced and lost a no-confidence vote within 13 days.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Prime Minister can be a member of which of the following?</t>
+          <t>Who among the following served as both Prime Minister and President of India?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Only Lok Sabha</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Only Rajya Sabha</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Any House</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Only Legislative Assembly</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Any House</t>
-        </is>
-      </c>
+          <t>V V Giri</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>PM can be from Lok Sabha or Rajya Sabha.</t>
+          <t>No one has held both posts; they are distinct positions.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What is the significance of the expression "pleasure of the President" in context of PM's tenure?</t>
+          <t>Who was the youngest Prime Minister of India?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Symbolic</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>President can remove at will</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PM can be dismissed anytime</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Depends on Lok Sabha majority</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Depends on Lok Sabha majority</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Though appointed by President, PM must enjoy majority support in Lok Sabha.</t>
+          <t>He became PM at the age of 40.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Who acted as Prime Minister in between Jawaharlal Nehru's death and Lal Bahadur Shastri's appointment?</t>
+          <t>Who was the first female Prime Minister of India?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
+          <t>Sushma Swaraj</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Gulzarilal Nanda</t>
-        </is>
-      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Meira Kumar</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>K Kamaraj</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>He served as interim PM after Nehru's death in 1964.</t>
+          <t>She became PM in 1966.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Prime Minister is described as which of the following?</t>
+          <t>Which committee is headed by the Prime Minister?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>First among equals</t>
+          <t>Public Accounts Committee</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Above all ministers</t>
+          <t>Estimates Committee</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Constitutional dictator</t>
+          <t>Planning Commission</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Presiding officer</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>First among equals</t>
+          <t>NITI Aayog</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>The PM is the keystone of the cabinet system and is the senior-most.</t>
+          <t>PM is the ex-officio Chairperson of NITI Aayog.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>When does the Prime Minister tender resignation?</t>
+          <t>The Prime Minister’s advisory role to the President is</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>After term completion</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>After President’s directive</t>
+          <t>Discretionary</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>After defeat in election</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>After losing Lok Sabha majority</t>
+          <t>Ceremonial</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>After losing Lok Sabha majority</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>If PM loses support, he must resign.</t>
+          <t>Under Article 74(1), advice of CoM led by PM is binding.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>If a Prime Minister is convicted in a criminal case and sentenced for more than 2 years, what happens?</t>
+          <t>Which Prime Minister had the longest uninterrupted tenure?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Can continue</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Disqualified immediately</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>President decides</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Can appeal to remain</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Disqualified immediately</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>As per RPA 1951 and SC rulings, such a person loses membership and hence PMship.</t>
+          <t>He served continuously for 17 years from 1947 to 1964.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Who can ask the Prime Minister to prove majority in Lok Sabha?</t>
+          <t>The Prime Minister is the leader of which house by convention?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Council of States</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Upper House</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>If doubt arises, President can ask PM to prove majority.</t>
+          <t>Although not mandatory, the PM usually leads the Lok Sabha.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which Prime Minister was in office when the Anti-Defection Law was passed?</t>
+          <t>Which Prime Minister’s government fell due to the withdrawal of support by AIADMK in 1999?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>IK Gujral</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>The 52nd Amendment Act, 1985 was passed during Rajiv Gandhi's tenure.</t>
+          <t>His government fell by one vote in 1999 after AIADMK withdrew support.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>If the Prime Minister is a member of Rajya Sabha, which of the following is true?</t>
+          <t>Which Prime Minister set up the Sarkaria Commission on Centre-State relations?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cannot take part in debates</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cannot vote in Lok Sabha</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cannot be PM</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Must resign from Rajya Sabha</t>
+          <t>P V Narasimha Rao</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cannot vote in Lok Sabha</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>A Rajya Sabha MP can participate but not vote in Lok Sabha.</t>
+          <t>The commission was set up in 1983 during his tenure.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which Prime Minister set up the Sarkaria Commission on Centre-State relations?</t>
+          <t>Which Prime Minister launched the 20-Point Programme in 1975?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
+          <t>Rajiv Gandhi</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Atal Bihari Vajpayee</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>Indira Gandhi</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Rajiv Gandhi</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Morarji Desai</t>
-        </is>
-      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>The commission was set up in 1983 during his tenure.</t>
+          <t>It was a socio-economic initiative launched during the Emergency.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Who was India’s first non-Congress Prime Minister?</t>
+          <t>If a Prime Minister is convicted in a criminal case and sentenced for more than 2 years, what happens?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Can continue</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Disqualified immediately</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>President decides</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>VP Singh</t>
+          <t>Can appeal to remain</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Disqualified immediately</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>He became PM in 1977 from the Janata Party.</t>
+          <t>As per RPA 1951 and SC rulings, such a person loses membership and hence PMship.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The Prime Minister’s Office (PMO) is</t>
+          <t>Which Prime Minister implemented the Green Revolution policies?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Statutory body</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Constitutional body</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Extra-constitutional body</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Judicial body</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Extra-constitutional body</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>The PMO is not mentioned in the Constitution but exists in practice.</t>
+          <t>Green Revolution was accelerated during her tenure.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Prime Minister is not mentioned by name in which part of the Constitution?</t>
+          <t>Which one of the following is not a function of the Prime Minister?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Part V</t>
+          <t>Allocating portfolios</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Part VI</t>
+          <t>Presiding over cabinet meetings</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>Dismissing ministers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Part IV</t>
+          <t>Advising President</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Part III</t>
+          <t>Dismissing ministers</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Fundamental Rights make no mention of the PM; it is dealt with in Part V (Union).</t>
+          <t>Only the President can formally dismiss ministers on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which Prime Minister initiated the policy of Economic Liberalization in India?</t>
+          <t>What is the position of the Prime Minister in the Union Cabinet?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Junior Minister</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Head of Cabinet</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>P V Narasimha Rao</t>
-        </is>
-      </c>
+          <t>Nominal Head</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>P V Narasimha Rao</t>
+          <t>Head of Cabinet</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>His government started reforms in 1991 with Manmohan Singh as Finance Minister.</t>
+          <t>The PM is the head and coordinates its functions.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The PM acts as a channel of communication between the President and</t>
+          <t>Which Prime Minister faced the most number of no-confidence motions?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>PM is the link between President and CoM as per Article 78.</t>
+          <t>She faced the most no-confidence motions during her tenure.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which PM was heading a coalition but completed a full 5-year term for the first time?</t>
+          <t>Which Prime Minister initiated the 'Look East Policy'?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>PV Narasimha Rao</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>IK Gujral</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>Atal Bihari Vajpayee</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>Manmohan Singh</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Atal Bihari Vajpayee</t>
-        </is>
-      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>PV Narasimha Rao</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>He led the NDA government from 1999–2004 successfully.</t>
+          <t>He initiated the policy to strengthen relations with Southeast Asia.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Who advises the President on the appointment of other ministers?</t>
+          <t>Which PM is associated with the Golden Quadrilateral highway project?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cabinet Secretary</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>President appoints ministers on advice of the PM.</t>
+          <t>The project was launched during his tenure as part of NHDP.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The Prime Minister is responsible to which body?</t>
+          <t>Which of the following committees is headed by the PM and deals with internal security?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Political Affairs Committee</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Appointments Committee</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Security Committee</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Cabinet Committee on Security</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Cabinet Committee on Security</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>The PM is collectively responsible to the Lok Sabha.</t>
+          <t>This committee deals with defense and internal security issues.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which Article of the Constitution deals with the Prime Minister?</t>
+          <t>How many times has the office of Prime Minister been held by someone from Rajya Sabha?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Article 78</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Article 75 provides for the appointment of the Prime Minister and other ministers.</t>
+          <t>Indira Gandhi, HD Deve Gowda, and Manmohan Singh have served while being Rajya Sabha members.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Under which circumstances can the Prime Minister recommend dissolution of Lok Sabha to the President?</t>
+          <t>The Prime Minister is the head of which body?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Only after a confidence vote</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Only with Cabinet approval</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Only after consulting Speaker</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Any time</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>The PM can advise dissolution anytime, subject to constitutional propriety.</t>
+          <t>The PM is the head of the Council of Ministers and leads the executive branch.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>During whose Prime Ministership was the Emergency declared in 1975?</t>
+          <t>Which Prime Minister's term saw the introduction of MGNREGA?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Narendra Modi</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>She declared Emergency under Article 352.</t>
+          <t>MGNREGA was launched in 2006 under his leadership.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which Prime Minister had the shortest tenure?</t>
+          <t>Which Prime Minister signed the Simla Agreement in 1972?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charan Singh</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Gulzarilal Nanda</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee (1996)</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee (1996)</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>He served for just 13 days before resigning.</t>
+          <t>It was signed with Pakistan after the 1971 war.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Who is known as the 'Father of Indian Economic Reforms'?</t>
+          <t>Who administers the oath of office to the Prime Minister?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PV Narasimha Rao</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>As Finance Minister in 1991, he launched liberalization reforms.</t>
+          <t>The President administers the oath of office and secrecy to the PM.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>How long can a person remain Prime Minister without being a member of either House of Parliament?</t>
+          <t>Who can ask the Prime Minister to prove majority in Lok Sabha?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Indefinitely</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>He/she must become a member within 6 months.</t>
+          <t>If doubt arises, President can ask PM to prove majority.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The resignation of the Prime Minister means the resignation of</t>
+          <t>Under which circumstances can the Prime Minister recommend dissolution of Lok Sabha to the President?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Only PM</t>
+          <t>Any time</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PM and Vice President</t>
+          <t>Only after a confidence vote</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Entire Council of Ministers</t>
+          <t>Only with Cabinet approval</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Only Cabinet Ministers</t>
+          <t>Only after consulting Speaker</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Entire Council of Ministers</t>
+          <t>Any time</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Since the PM is head, his resignation dissolves the Council.</t>
+          <t>The PM can advise dissolution anytime, subject to constitutional propriety.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which constitutional article allows the PM to recommend President's Rule in a state?</t>
+          <t>Who served as PM after the assassination of Indira Gandhi?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Article 365</t>
+          <t>Gulzarilal Nanda</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>It allows the President to impose President’s Rule based on Governor’s or PM’s recommendation.</t>
+          <t>He was immediately sworn in after her assassination in 1984.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>What is the tenure of Prime Minister of India?</t>
+          <t>Which PM was awarded the Bharat Ratna posthumously in 1991?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fixed 5 years</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Fixed 6 years</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Depends on President</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>No fixed tenure</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>No fixed tenure</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>PM holds office during the pleasure of the President, as long as majority is maintained.</t>
+          <t>He was assassinated in 1991 and awarded the Bharat Ratna posthumously.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which of the following committees is headed by the PM and deals with internal security?</t>
+          <t>Under which constitutional amendment is the advice of the Council of Ministers to the President made binding?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Political Affairs Committee</t>
+          <t>38th Amendment</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Appointments Committee</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Security Committee</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cabinet Committee on Security</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cabinet Committee on Security</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>This committee deals with defense and internal security issues.</t>
+          <t>The 42nd Amendment (1976) made Presidential advice binding.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Who among the following served as both Prime Minister and President of India?</t>
+          <t>In which year was the post of Deputy Prime Minister first created in India?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Morarji Desai</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>V V Giri</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>No one has held both posts; they are distinct positions.</t>
+          <t>Sardar Vallabhbhai Patel was the first Deputy PM in 1947.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>If the Prime Minister dies suddenly, who becomes the Acting PM?</t>
+          <t>Which Prime Minister was a recipient of Bharat Ratna before becoming PM?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Senior-most Cabinet Minister</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Home Minister</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>No provision</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Senior-most Cabinet Minister</t>
+          <t>Morarji Desai</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Conventionally, the senior-most is asked to act until a new leader is chosen.</t>
+          <t>He received Bharat Ratna in 1991, after retirement.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which Prime Minister’s government fell due to the withdrawal of support by AIADMK in 1999?</t>
+          <t>The PM acts as a channel of communication between the President and</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>IK Gujral</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>HD Deve Gowda</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Atal Bihari Vajpayee</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>His government fell by one vote in 1999 after AIADMK withdrew support.</t>
+          <t>PM is the link between President and CoM as per Article 78.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>What is the difference between Cabinet and Council of Ministers in context of PM’s role?</t>
+          <t>Which Prime Minister gave the slogan 'Garibi Hatao'?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>No difference</t>
+          <t>Rajiv Gandhi</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cabinet is a part of CoM</t>
+          <t>Lal Bahadur Shastri</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PM heads Cabinet only</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Only Cabinet advises President</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cabinet is a part of CoM</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>PM leads both, but Cabinet is an inner core of senior ministers.</t>
+          <t>She gave this slogan during the 1971 election campaign.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which Prime Minister gave the slogan 'Garibi Hatao'?</t>
+          <t>Which PM was heading a coalition but completed a full 5-year term for the first time?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Rajiv Gandhi</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Lal Bahadur Shastri</t>
+          <t>IK Gujral</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Atal Bihari Vajpayee</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>She gave this slogan during the 1971 election campaign.</t>
+          <t>He led the NDA government from 1999–2004 successfully.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>The Prime Minister communicates to the President all decisions of the Council of Ministers under which Article?</t>
+          <t>What happens if the Prime Minister loses majority support in Lok Sabha?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Dismissed by President</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Article 78</t>
+          <t>Resigns</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Continues till term ends</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>Impeached</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Article 78</t>
+          <t>Resigns</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>It is the duty of the PM to inform the President of all cabinet decisions.</t>
+          <t>Losing majority means the PM must resign.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which committee is headed by the Prime Minister?</t>
+          <t>Which PM led the Janata Dal government formed after the Mandal Commission recommendations?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Public Accounts Committee</t>
+          <t>Charan Singh</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Estimates Committee</t>
+          <t>HD Deve Gowda</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Planning Commission</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>IK Gujral</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>NITI Aayog</t>
+          <t>VP Singh</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>PM is the ex-officio Chairperson of NITI Aayog.</t>
+          <t>He implemented the Mandal Commission recommendations in 1990.</t>
         </is>
       </c>
     </row>
